--- a/AAII_Financials/Quarterly/NIC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NIC_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="92">
   <si>
     <t>NIC</t>
   </si>
@@ -656,124 +656,130 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>103500</v>
+      </c>
+      <c r="E8" s="3">
         <v>99900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>92100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>87400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>85800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>70700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>59500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>57900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>57600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>38700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>38300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>36900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>38000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>37300</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -816,8 +822,11 @@
       <c r="P9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -860,8 +869,11 @@
       <c r="P10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -878,8 +890,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -922,8 +935,11 @@
       <c r="P12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -966,8 +982,11 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1010,52 +1029,58 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E15" s="3">
         <v>-2000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>-2100</v>
-      </c>
-      <c r="F15" s="3">
-        <v>-2200</v>
       </c>
       <c r="G15" s="3">
         <v>-2200</v>
       </c>
       <c r="H15" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="I15" s="3">
         <v>-1600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>-1300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>-1400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-1100</v>
-      </c>
-      <c r="L15" s="3">
-        <v>-800</v>
       </c>
       <c r="M15" s="3">
         <v>-800</v>
       </c>
       <c r="N15" s="3">
-        <v>-900</v>
+        <v>-800</v>
       </c>
       <c r="O15" s="3">
         <v>-900</v>
       </c>
       <c r="P15" s="3">
+        <v>-900</v>
+      </c>
+      <c r="Q15" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1069,96 +1094,103 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>40300</v>
+      </c>
+      <c r="E17" s="3">
         <v>38900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>33500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>33700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>19500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>16300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>63200</v>
+      </c>
+      <c r="E18" s="3">
         <v>61000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>58600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>53700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>66300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>54400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>54300</v>
-      </c>
-      <c r="J18" s="3">
-        <v>53500</v>
       </c>
       <c r="K18" s="3">
         <v>53500</v>
       </c>
       <c r="L18" s="3">
+        <v>53500</v>
+      </c>
+      <c r="M18" s="3">
         <v>35100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>35600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>33700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>34000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>32600</v>
       </c>
     </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1175,96 +1207,103 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-25800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-29200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-28200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-66700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-29200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-29500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-22400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-21600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-31700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-25000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-10600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-9500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-9800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>42700</v>
+      </c>
+      <c r="E21" s="3">
         <v>35700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>35600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-8900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>42000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>30000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>37000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>38700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>26400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>14200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>27500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>26900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>27400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>27200</v>
       </c>
     </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1307,96 +1346,105 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>37400</v>
+      </c>
+      <c r="E23" s="3">
         <v>31800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>30500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-13100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>37100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>24800</v>
-      </c>
-      <c r="I23" s="3">
-        <v>31900</v>
       </c>
       <c r="J23" s="3">
         <v>31900</v>
       </c>
       <c r="K23" s="3">
+        <v>31900</v>
+      </c>
+      <c r="L23" s="3">
         <v>21800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>10100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>25000</v>
-      </c>
-      <c r="N23" s="3">
-        <v>24200</v>
       </c>
       <c r="O23" s="3">
         <v>24200</v>
       </c>
       <c r="P23" s="3">
+        <v>24200</v>
+      </c>
+      <c r="Q23" s="3">
         <v>24600</v>
       </c>
     </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E24" s="3">
         <v>14700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>7900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-4200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>9500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>6300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>7900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>7700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>6700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>5900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>6100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>6400</v>
       </c>
     </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1439,96 +1487,105 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>30700</v>
+      </c>
+      <c r="E26" s="3">
         <v>17200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>22600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-8900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>27600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>18500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>24000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>24200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>16300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>7800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>18300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>18200</v>
-      </c>
-      <c r="O26" s="3">
-        <v>18100</v>
       </c>
       <c r="P26" s="3">
         <v>18100</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3">
+        <v>18100</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>30700</v>
+      </c>
+      <c r="E27" s="3">
         <v>17200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>22600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-8900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>27600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>18500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>24000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>24200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>16300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>7800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>18300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>18200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>18000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1571,8 +1628,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1615,8 +1675,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1659,8 +1722,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1703,96 +1769,105 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>25800</v>
+      </c>
+      <c r="E32" s="3">
         <v>29200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>28200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>66700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>29200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>29500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>22400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>21600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>31700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>25000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>10600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>9500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>9800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>8000</v>
       </c>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>30700</v>
+      </c>
+      <c r="E33" s="3">
         <v>17200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>22600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-8900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>27600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>18500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>24000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>24200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>16300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>7800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>18300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>18200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>18000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1835,101 +1910,110 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>30700</v>
+      </c>
+      <c r="E35" s="3">
         <v>17200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>22600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-8900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>27600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>18500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>24000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>24200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>16300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>7800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>18300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>18200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>18000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1946,8 +2030,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1964,96 +2049,103 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>136300</v>
+      </c>
+      <c r="E41" s="3">
         <v>117000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>131800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>104800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>133700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>132000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>111700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>203400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>231300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>241700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>101000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>88600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>118000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>100900</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>419100</v>
+      </c>
+      <c r="E42" s="3">
         <v>494800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>440800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>78200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>98800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>399000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>138100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>266500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>430000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1171600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>748200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>702800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>742000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>812300</v>
       </c>
     </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2096,8 +2188,11 @@
       <c r="P43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2140,8 +2235,11 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2184,8 +2282,11 @@
       <c r="P45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2228,8 +2329,11 @@
       <c r="P46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2272,96 +2376,105 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>118800</v>
+      </c>
+      <c r="E48" s="3">
         <v>117700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>117300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>112600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>109000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>106600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>96700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>94300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>94600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>83500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>61600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>59400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>59900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>64200</v>
       </c>
     </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>406000</v>
+      </c>
+      <c r="E49" s="3">
         <v>408100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>410400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>412800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>415500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>426500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>350600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>351900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>353100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>283100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>185200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>185400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>185600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>185700</v>
       </c>
     </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2404,8 +2517,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2448,8 +2564,11 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2492,8 +2611,11 @@
       <c r="P52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2536,52 +2658,58 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8468700</v>
+      </c>
+      <c r="E54" s="3">
         <v>8416200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8482600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8192400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8764000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8895900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7370300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7320200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7695000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6407800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4587300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4543800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4551800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4706400</v>
       </c>
     </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2598,8 +2726,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2616,52 +2745,56 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>64900</v>
+      </c>
+      <c r="E57" s="3">
         <v>61600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>58800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>54500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>70200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>56300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>47600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>45800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>68700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>58000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>43800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>49200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>48300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>48900</v>
       </c>
     </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2704,8 +2837,11 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2748,8 +2884,11 @@
       <c r="P59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2792,52 +2931,58 @@
       <c r="P60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>161900</v>
+      </c>
+      <c r="E61" s="3">
         <v>192800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>192600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>192400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>192300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>192200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>192000</v>
-      </c>
-      <c r="J61" s="3">
-        <v>191900</v>
       </c>
       <c r="K61" s="3">
         <v>191900</v>
       </c>
       <c r="L61" s="3">
+        <v>191900</v>
+      </c>
+      <c r="M61" s="3">
         <v>124200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>25100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>25000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>24900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>376800</v>
       </c>
     </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2880,8 +3025,11 @@
       <c r="P62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2924,8 +3072,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2968,8 +3119,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3012,52 +3166,58 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7429700</v>
+      </c>
+      <c r="E66" s="3">
         <v>7441700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7505000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7230600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7791400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7957500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6530900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6483900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6803100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5678500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4028000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3993800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4012600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4168300</v>
       </c>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3074,8 +3234,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3118,8 +3279,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3162,8 +3326,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3206,8 +3373,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3250,52 +3420,58 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>458300</v>
+      </c>
+      <c r="E72" s="3">
         <v>431300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>417900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>399000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>407900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>380300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>361800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>337800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>313600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>297300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>289500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>271200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>253000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>235000</v>
       </c>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3338,8 +3514,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3382,8 +3561,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3426,52 +3608,58 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1039000</v>
+      </c>
+      <c r="E76" s="3">
         <v>974500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>977600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>961800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>972500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>938500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>839400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>836300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>891900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>729300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>559400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>550000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>539200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>538100</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3514,101 +3702,110 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>30700</v>
+      </c>
+      <c r="E81" s="3">
         <v>17200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>22600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-8900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>27600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>18500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>24000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>24200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>16300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>7800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>18300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>18200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>18000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3625,52 +3822,56 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E83" s="3">
         <v>3900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>5100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>5000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>6800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>3100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3713,8 +3914,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3757,8 +3961,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3801,8 +4008,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3845,8 +4055,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3889,52 +4102,58 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>37800</v>
+      </c>
+      <c r="E89" s="3">
         <v>21800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>32800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>15500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>30000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>38000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>27400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>21900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>45400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>9200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>4800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>38200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>14600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>44100</v>
       </c>
     </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3951,52 +4170,56 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-6900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5900</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-3200</v>
       </c>
       <c r="M91" s="3">
         <v>-3200</v>
       </c>
       <c r="N91" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="O91" s="3">
         <v>-500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4039,8 +4262,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4083,52 +4309,58 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-78700</v>
+      </c>
+      <c r="E94" s="3">
         <v>88700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>92700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>488800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-134500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-169600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-283100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>70900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-637600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>324600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>24600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-82200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>109700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-19200</v>
       </c>
     </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4145,8 +4377,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4154,7 +4387,7 @@
         <v>-3700</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>-3700</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>
@@ -4189,8 +4422,11 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4233,8 +4469,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4277,8 +4516,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4321,52 +4563,58 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-69900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>265500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-544900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-179100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>388900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>40800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-292200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-163100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>224300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>27200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-23100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-175000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4409,48 +4657,54 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-54400</v>
+      </c>
+      <c r="E102" s="3">
         <v>40700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>391000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-40500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-283600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>257300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-214900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-199400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-755300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>558200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>56600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-67000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-50700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>30900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NIC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NIC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
   <si>
     <t>NIC</t>
   </si>
@@ -656,130 +656,137 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>104000</v>
+      </c>
+      <c r="E8" s="3">
         <v>103500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>99900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>92100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>87400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>85800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>70700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>59500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>57900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>57600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>38700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>38300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>36900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>38000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>37300</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -825,8 +832,11 @@
       <c r="Q9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -872,8 +882,11 @@
       <c r="Q10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -891,8 +904,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -938,8 +952,11 @@
       <c r="Q12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -985,8 +1002,11 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1032,8 +1052,11 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1041,46 +1064,49 @@
         <v>-1800</v>
       </c>
       <c r="E15" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F15" s="3">
         <v>-2000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>-2100</v>
-      </c>
-      <c r="G15" s="3">
-        <v>-2200</v>
       </c>
       <c r="H15" s="3">
         <v>-2200</v>
       </c>
       <c r="I15" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="J15" s="3">
         <v>-1600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>-1300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-1400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-1100</v>
-      </c>
-      <c r="M15" s="3">
-        <v>-800</v>
       </c>
       <c r="N15" s="3">
         <v>-800</v>
       </c>
       <c r="O15" s="3">
-        <v>-900</v>
+        <v>-800</v>
       </c>
       <c r="P15" s="3">
         <v>-900</v>
       </c>
       <c r="Q15" s="3">
+        <v>-900</v>
+      </c>
+      <c r="R15" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1095,102 +1121,109 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>42000</v>
+      </c>
+      <c r="E17" s="3">
         <v>40300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>38900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>33500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>33700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>19500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>16300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>62000</v>
+      </c>
+      <c r="E18" s="3">
         <v>63200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>61000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>58600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>53700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>66300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>54400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>54300</v>
-      </c>
-      <c r="K18" s="3">
-        <v>53500</v>
       </c>
       <c r="L18" s="3">
         <v>53500</v>
       </c>
       <c r="M18" s="3">
+        <v>53500</v>
+      </c>
+      <c r="N18" s="3">
         <v>35100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>35600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>33700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>34000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>32600</v>
       </c>
     </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1208,102 +1241,109 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-27700</v>
+      </c>
+      <c r="E20" s="3">
         <v>-25800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-29200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-28200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-66700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-29200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-29500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-22400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-21600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-31700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-25000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-10600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-9500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>39100</v>
+      </c>
+      <c r="E21" s="3">
         <v>42700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>35700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>35600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-8900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>42000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>30000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>37000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>38700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>26400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>14200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>27500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>26900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>27400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>27200</v>
       </c>
     </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1349,102 +1389,111 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>34300</v>
+      </c>
+      <c r="E23" s="3">
         <v>37400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>31800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>30500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-13100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>37100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>24800</v>
-      </c>
-      <c r="J23" s="3">
-        <v>31900</v>
       </c>
       <c r="K23" s="3">
         <v>31900</v>
       </c>
       <c r="L23" s="3">
+        <v>31900</v>
+      </c>
+      <c r="M23" s="3">
         <v>21800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>10100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>25000</v>
-      </c>
-      <c r="O23" s="3">
-        <v>24200</v>
       </c>
       <c r="P23" s="3">
         <v>24200</v>
       </c>
       <c r="Q23" s="3">
+        <v>24200</v>
+      </c>
+      <c r="R23" s="3">
         <v>24600</v>
       </c>
     </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E24" s="3">
         <v>6800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>14700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>7900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-4200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>9500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>6300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>7900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>7700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>6700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>5900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>6100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>6400</v>
       </c>
     </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1490,102 +1539,111 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>27800</v>
+      </c>
+      <c r="E26" s="3">
         <v>30700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>17200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>22600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-8900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>27600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>18500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>24000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>24200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>16300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>7800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>18300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>18200</v>
-      </c>
-      <c r="P26" s="3">
-        <v>18100</v>
       </c>
       <c r="Q26" s="3">
         <v>18100</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3">
+        <v>18100</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>27800</v>
+      </c>
+      <c r="E27" s="3">
         <v>30700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>17200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>22600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-8900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>27600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>18500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>24000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>24200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>16300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>7800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>18300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>18200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>18000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1631,8 +1689,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1678,8 +1739,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1725,8 +1789,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1772,102 +1839,111 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>27700</v>
+      </c>
+      <c r="E32" s="3">
         <v>25800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>29200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>28200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>66700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>29200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>29500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>22400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>21600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>31700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>25000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>10600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>9500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>9800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>8000</v>
       </c>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>27800</v>
+      </c>
+      <c r="E33" s="3">
         <v>30700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>17200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>22600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-8900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>27600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>18500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>24000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>24200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>16300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>7800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>18300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>18200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>18000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1913,107 +1989,116 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>27800</v>
+      </c>
+      <c r="E35" s="3">
         <v>30700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>17200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>22600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-8900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>27600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>18500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>24000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>24200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>16300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>7800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>18300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>18200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>18000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2031,8 +2116,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2050,102 +2136,109 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>87300</v>
+      </c>
+      <c r="E41" s="3">
         <v>136300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>117000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>131800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>104800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>133700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>132000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>111700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>203400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>231300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>241700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>101000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>88600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>118000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>100900</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>406200</v>
+      </c>
+      <c r="E42" s="3">
         <v>419100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>494800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>440800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>78200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>98800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>399000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>138100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>266500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>430000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1171600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>748200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>702800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>742000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>812300</v>
       </c>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2191,8 +2284,11 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2238,8 +2334,11 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2285,8 +2384,11 @@
       <c r="Q45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2332,8 +2434,11 @@
       <c r="Q46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2379,102 +2484,111 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>120000</v>
+      </c>
+      <c r="E48" s="3">
         <v>118800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>117700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>117300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>112600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>109000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>106600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>96700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>94300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>94600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>83500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>61600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>59400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>59900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>64200</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>404400</v>
+      </c>
+      <c r="E49" s="3">
         <v>406000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>408100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>410400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>412800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>415500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>426500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>350600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>351900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>353100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>283100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>185200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>185400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>185600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>185700</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2520,8 +2634,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2567,8 +2684,11 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2614,8 +2734,11 @@
       <c r="Q52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2661,55 +2784,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8446700</v>
+      </c>
+      <c r="E54" s="3">
         <v>8468700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8416200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8482600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8192400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8764000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8895900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7370300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7320200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7695000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6407800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4587300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4543800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4551800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4706400</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2727,8 +2856,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2746,55 +2876,59 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>55000</v>
+      </c>
+      <c r="E57" s="3">
         <v>64900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>61600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>58800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>54500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>70200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>56300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>47600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>45800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>68700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>58000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>43800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>49200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>48300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>48900</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2840,8 +2974,11 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2887,8 +3024,11 @@
       <c r="Q59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2934,55 +3074,61 @@
       <c r="Q60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>157300</v>
+      </c>
+      <c r="E61" s="3">
         <v>161900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>192800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>192600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>192400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>192300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>192200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>192000</v>
-      </c>
-      <c r="K61" s="3">
-        <v>191900</v>
       </c>
       <c r="L61" s="3">
         <v>191900</v>
       </c>
       <c r="M61" s="3">
+        <v>191900</v>
+      </c>
+      <c r="N61" s="3">
         <v>124200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>25100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>25000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>24900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>376800</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3028,8 +3174,11 @@
       <c r="Q62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3075,8 +3224,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3122,8 +3274,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3169,55 +3324,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7383000</v>
+      </c>
+      <c r="E66" s="3">
         <v>7429700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7441700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7505000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7230600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7791400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7957500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6530900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6483900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6803100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5678500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4028000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3993800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4012600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4168300</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3235,8 +3396,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3282,8 +3444,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3329,8 +3494,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3376,8 +3544,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3423,55 +3594,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>482300</v>
+      </c>
+      <c r="E72" s="3">
         <v>458300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>431300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>417900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>399000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>407900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>380300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>361800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>337800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>313600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>297300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>289500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>271200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>253000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>235000</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3517,8 +3694,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3564,8 +3744,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3611,55 +3794,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1063700</v>
+      </c>
+      <c r="E76" s="3">
         <v>1039000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>974500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>977600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>961800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>972500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>938500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>839400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>836300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>891900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>729300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>559400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>550000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>539200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>538100</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3705,107 +3894,116 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>27800</v>
+      </c>
+      <c r="E81" s="3">
         <v>30700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>17200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>22600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-8900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>27600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>18500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>24000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>24200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>16300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>7800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>18300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>18200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>18000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3823,55 +4021,59 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E83" s="3">
         <v>5200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>5100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>5200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>5000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>6800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>3100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3917,8 +4119,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3964,8 +4169,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4011,8 +4219,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4058,8 +4269,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4105,55 +4319,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>23400</v>
+      </c>
+      <c r="E89" s="3">
         <v>37800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>21800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>32800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>15500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>30000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>38000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>27400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>21900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>45400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>9200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>4800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>38200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>14600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>44100</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4171,55 +4391,59 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5900</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-3200</v>
       </c>
       <c r="N91" s="3">
         <v>-3200</v>
       </c>
       <c r="O91" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="P91" s="3">
         <v>-500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4265,8 +4489,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4312,55 +4539,61 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-49000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-78700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>88700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>92700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>488800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-134500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-169600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-283100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>70900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-637600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>324600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>24600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-82200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>109700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-19200</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4378,19 +4611,20 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-3700</v>
+        <v>-3800</v>
       </c>
       <c r="E96" s="3">
         <v>-3700</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>-3700</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
@@ -4425,8 +4659,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4472,8 +4709,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4519,8 +4759,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4566,55 +4809,61 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-38400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-13500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-69900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>265500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-544900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-179100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>388900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>40800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-292200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-163100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>224300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>27200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-23100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-175000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4660,51 +4909,57 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-64000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-54400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>40700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>391000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-40500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-283600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>257300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-214900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-199400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-755300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>558200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>56600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-67000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-50700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>30900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NIC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NIC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="92">
   <si>
     <t>NIC</t>
   </si>
@@ -656,137 +656,144 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>108900</v>
+      </c>
+      <c r="E8" s="3">
         <v>104000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>103500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>99900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>92100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>87400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>85800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>70700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>59500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>57900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>57600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>38700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>38300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>36900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>38000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>37300</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -835,8 +842,11 @@
       <c r="R9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -885,8 +895,11 @@
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -905,8 +918,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -955,8 +969,11 @@
       <c r="R12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1005,8 +1022,11 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1055,8 +1075,11 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1067,46 +1090,49 @@
         <v>-1800</v>
       </c>
       <c r="F15" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="G15" s="3">
         <v>-2000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>-2100</v>
-      </c>
-      <c r="H15" s="3">
-        <v>-2200</v>
       </c>
       <c r="I15" s="3">
         <v>-2200</v>
       </c>
       <c r="J15" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="K15" s="3">
         <v>-1600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-1300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-1400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-1100</v>
-      </c>
-      <c r="N15" s="3">
-        <v>-800</v>
       </c>
       <c r="O15" s="3">
         <v>-800</v>
       </c>
       <c r="P15" s="3">
-        <v>-900</v>
+        <v>-800</v>
       </c>
       <c r="Q15" s="3">
         <v>-900</v>
       </c>
       <c r="R15" s="3">
+        <v>-900</v>
+      </c>
+      <c r="S15" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1122,108 +1148,115 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>44900</v>
+      </c>
+      <c r="E17" s="3">
         <v>42000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>40300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>38900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>33500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>33700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>19500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>16300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>64000</v>
+      </c>
+      <c r="E18" s="3">
         <v>62000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>63200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>61000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>58600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>53700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>66300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>54400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>54300</v>
-      </c>
-      <c r="L18" s="3">
-        <v>53500</v>
       </c>
       <c r="M18" s="3">
         <v>53500</v>
       </c>
       <c r="N18" s="3">
+        <v>53500</v>
+      </c>
+      <c r="O18" s="3">
         <v>35100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>35600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>33700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>34000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>32600</v>
       </c>
     </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1242,108 +1275,115 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-27300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-27700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-25800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-29200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-28200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-66700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-29200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-29500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-22400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-21600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-31700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-25000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-10600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-9500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-9800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>41200</v>
+      </c>
+      <c r="E21" s="3">
         <v>39100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>42700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>35700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>35600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-8900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>42000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>30000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>37000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>38700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>26400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>14200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>27500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>26900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>27400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>27200</v>
       </c>
     </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1392,108 +1432,117 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>36700</v>
+      </c>
+      <c r="E23" s="3">
         <v>34300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>37400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>31800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>30500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-13100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>37100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>24800</v>
-      </c>
-      <c r="K23" s="3">
-        <v>31900</v>
       </c>
       <c r="L23" s="3">
         <v>31900</v>
       </c>
       <c r="M23" s="3">
+        <v>31900</v>
+      </c>
+      <c r="N23" s="3">
         <v>21800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>10100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>25000</v>
-      </c>
-      <c r="P23" s="3">
-        <v>24200</v>
       </c>
       <c r="Q23" s="3">
         <v>24200</v>
       </c>
       <c r="R23" s="3">
+        <v>24200</v>
+      </c>
+      <c r="S23" s="3">
         <v>24600</v>
       </c>
     </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E24" s="3">
         <v>6500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>6800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>14700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>7900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-4200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>9500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>6300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>7900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>7700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>5500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>6700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>5900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>6100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>6400</v>
       </c>
     </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1542,108 +1591,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>29300</v>
+      </c>
+      <c r="E26" s="3">
         <v>27800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>30700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>17200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>22600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-8900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>27600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>18500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>24000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>24200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>16300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>7800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>18300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>18200</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>18100</v>
       </c>
       <c r="R26" s="3">
         <v>18100</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3">
+        <v>18100</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>29300</v>
+      </c>
+      <c r="E27" s="3">
         <v>27800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>30700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>17200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>22600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-8900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>27600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>18500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>24000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>24200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>16300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>7800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>18300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>18200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>18000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1692,8 +1750,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1742,8 +1803,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1792,8 +1856,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1842,108 +1909,117 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>27300</v>
+      </c>
+      <c r="E32" s="3">
         <v>27700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>25800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>29200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>28200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>66700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>29200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>29500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>22400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>21600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>31700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>25000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>10600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>9500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>9800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>8000</v>
       </c>
     </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>29300</v>
+      </c>
+      <c r="E33" s="3">
         <v>27800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>30700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>17200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>22600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-8900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>27600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>18500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>24000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>24200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>16300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>7800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>18300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>18200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>18000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1992,113 +2068,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>29300</v>
+      </c>
+      <c r="E35" s="3">
         <v>27800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>30700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>17200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>22600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-8900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>27600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>18500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>24000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>24200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>16300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>7800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>18300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>18200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>18000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2117,8 +2202,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2137,108 +2223,115 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>113600</v>
+      </c>
+      <c r="E41" s="3">
         <v>87300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>136300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>117000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>131800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>104800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>133700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>132000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>111700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>203400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>231300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>241700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>101000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>88600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>118000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>100900</v>
       </c>
     </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>359700</v>
+      </c>
+      <c r="E42" s="3">
         <v>406200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>419100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>494800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>440800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>78200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>98800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>399000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>138100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>266500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>430000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1171600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>748200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>702800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>742000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>812300</v>
       </c>
     </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2287,8 +2380,11 @@
       <c r="R43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2337,8 +2433,11 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2387,8 +2486,11 @@
       <c r="R45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2437,8 +2539,11 @@
       <c r="R46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2487,108 +2592,117 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>121000</v>
+      </c>
+      <c r="E48" s="3">
         <v>120000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>118800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>117700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>117300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>112600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>109000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>106600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>96700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>94300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>94600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>83500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>61600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>59400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>59900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>64200</v>
       </c>
     </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>402400</v>
+      </c>
+      <c r="E49" s="3">
         <v>404400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>406000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>408100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>410400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>412800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>415500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>426500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>350600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>351900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>353100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>283100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>185200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>185400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>185600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>185700</v>
       </c>
     </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2637,8 +2751,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2687,8 +2804,11 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2737,8 +2857,11 @@
       <c r="R52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2787,58 +2910,64 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8557000</v>
+      </c>
+      <c r="E54" s="3">
         <v>8446700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8468700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8416200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8482600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8192400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8764000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8895900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7370300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7320200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7695000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6407800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4587300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4543800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4551800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4706400</v>
       </c>
     </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2857,8 +2986,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2877,58 +3007,62 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>62100</v>
+      </c>
+      <c r="E57" s="3">
         <v>55000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>64900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>61600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>58800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>54500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>70200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>56300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>47600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>45800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>68700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>58000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>43800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>49200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>48300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>48900</v>
       </c>
     </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2977,8 +3111,11 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3027,8 +3164,11 @@
       <c r="R59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3077,58 +3217,64 @@
       <c r="R60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>157400</v>
+      </c>
+      <c r="E61" s="3">
         <v>157300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>161900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>192800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>192600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>192400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>192300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>192200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>192000</v>
-      </c>
-      <c r="L61" s="3">
-        <v>191900</v>
       </c>
       <c r="M61" s="3">
         <v>191900</v>
       </c>
       <c r="N61" s="3">
+        <v>191900</v>
+      </c>
+      <c r="O61" s="3">
         <v>124200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>25100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>25000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>24900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>376800</v>
       </c>
     </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3177,8 +3323,11 @@
       <c r="R62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3227,8 +3376,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3277,8 +3429,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3327,58 +3482,64 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7465600</v>
+      </c>
+      <c r="E66" s="3">
         <v>7383000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7429700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7441700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7505000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7230600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7791400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7957500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6530900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6483900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6803100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5678500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4028000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3993800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4012600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4168300</v>
       </c>
     </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3397,8 +3558,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3447,8 +3609,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3497,8 +3662,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3547,8 +3715,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3597,58 +3768,64 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>507400</v>
+      </c>
+      <c r="E72" s="3">
         <v>482300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>458300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>431300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>417900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>399000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>407900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>380300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>361800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>337800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>313600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>297300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>289500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>271200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>253000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>235000</v>
       </c>
     </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3697,8 +3874,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3747,8 +3927,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3797,58 +3980,64 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1091400</v>
+      </c>
+      <c r="E76" s="3">
         <v>1063700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1039000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>974500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>977600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>961800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>972500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>938500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>839400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>836300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>891900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>729300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>559400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>550000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>539200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>538100</v>
       </c>
     </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3897,113 +4086,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>29300</v>
+      </c>
+      <c r="E81" s="3">
         <v>27800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>30700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>17200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>22600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-8900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>27600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>18500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>24000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>24200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>16300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>7800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>18300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>18200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>18000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4022,58 +4220,62 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E83" s="3">
         <v>4800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>5200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>5100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>5200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>6800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>3100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4122,8 +4324,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4172,8 +4377,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4222,8 +4430,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4272,8 +4483,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4322,58 +4536,64 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>37300</v>
+      </c>
+      <c r="E89" s="3">
         <v>23400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>37800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>21800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>32800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>15500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>30000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>38000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>27400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>21900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>45400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>9200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>4800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>38200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>14600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>44100</v>
       </c>
     </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4392,58 +4612,62 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-6900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5900</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-3200</v>
       </c>
       <c r="O91" s="3">
         <v>-3200</v>
       </c>
       <c r="P91" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4492,8 +4716,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4542,58 +4769,64 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-127700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-49000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-78700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>88700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>92700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>488800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-134500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-169600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-283100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>70900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-637600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>324600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>24600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-82200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>109700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-19200</v>
       </c>
     </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4612,22 +4845,23 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E96" s="3">
         <v>-3800</v>
-      </c>
-      <c r="E96" s="3">
-        <v>-3700</v>
       </c>
       <c r="F96" s="3">
         <v>-3700</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>-3700</v>
       </c>
       <c r="H96" s="3">
         <v>0</v>
@@ -4662,8 +4896,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4712,8 +4949,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4762,8 +5002,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4812,58 +5055,64 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>71500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-38400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-13500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-69900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>265500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-544900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-179100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>388900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>40800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-292200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-163100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>224300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>27200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-23100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-175000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4912,54 +5161,60 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-18900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-64000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-54400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>40700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>391000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-40500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-283600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>257300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-214900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-199400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-755300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>558200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>56600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-67000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-50700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>30900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NIC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NIC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="92">
   <si>
     <t>NIC</t>
   </si>
@@ -656,144 +656,151 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>108900</v>
+        <v>90000</v>
       </c>
       <c r="E8" s="3">
-        <v>104000</v>
+        <v>83600</v>
       </c>
       <c r="F8" s="3">
-        <v>103500</v>
+        <v>81500</v>
       </c>
       <c r="G8" s="3">
-        <v>99900</v>
+        <v>87700</v>
       </c>
       <c r="H8" s="3">
-        <v>92100</v>
+        <v>77600</v>
       </c>
       <c r="I8" s="3">
-        <v>87400</v>
+        <v>75400</v>
       </c>
       <c r="J8" s="3">
+        <v>31800</v>
+      </c>
+      <c r="K8" s="3">
         <v>85800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>70700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>59500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>57900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>57600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>38700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>38300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>36900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>38000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>37300</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -845,31 +852,34 @@
       <c r="S9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>90000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>83600</v>
+      </c>
+      <c r="F10" s="3">
+        <v>81500</v>
+      </c>
+      <c r="G10" s="3">
+        <v>87700</v>
+      </c>
+      <c r="H10" s="3">
+        <v>77600</v>
+      </c>
+      <c r="I10" s="3">
+        <v>75400</v>
+      </c>
+      <c r="J10" s="3">
+        <v>31800</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -898,8 +908,11 @@
       <c r="S10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -919,8 +932,9 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -972,8 +986,11 @@
       <c r="S12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1025,31 +1042,34 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1078,61 +1098,67 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-1800</v>
+        <v>4400</v>
       </c>
       <c r="E15" s="3">
-        <v>-1800</v>
+        <v>4400</v>
       </c>
       <c r="F15" s="3">
-        <v>-1800</v>
+        <v>4800</v>
       </c>
       <c r="G15" s="3">
-        <v>-2000</v>
+        <v>6100</v>
       </c>
       <c r="H15" s="3">
-        <v>-2100</v>
+        <v>3900</v>
       </c>
       <c r="I15" s="3">
+        <v>5100</v>
+      </c>
+      <c r="J15" s="3">
+        <v>4200</v>
+      </c>
+      <c r="K15" s="3">
         <v>-2200</v>
       </c>
-      <c r="J15" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-1600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-1300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-1400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-1100</v>
-      </c>
-      <c r="O15" s="3">
-        <v>-800</v>
       </c>
       <c r="P15" s="3">
         <v>-800</v>
       </c>
       <c r="Q15" s="3">
-        <v>-900</v>
+        <v>-800</v>
       </c>
       <c r="R15" s="3">
         <v>-900</v>
       </c>
       <c r="S15" s="3">
+        <v>-900</v>
+      </c>
+      <c r="T15" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1149,114 +1175,121 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>44900</v>
+        <v>46500</v>
       </c>
       <c r="E17" s="3">
+        <v>44100</v>
+      </c>
+      <c r="F17" s="3">
+        <v>44300</v>
+      </c>
+      <c r="G17" s="3">
+        <v>47500</v>
+      </c>
+      <c r="H17" s="3">
+        <v>42300</v>
+      </c>
+      <c r="I17" s="3">
+        <v>41800</v>
+      </c>
+      <c r="J17" s="3">
         <v>42000</v>
       </c>
-      <c r="F17" s="3">
-        <v>40300</v>
-      </c>
-      <c r="G17" s="3">
-        <v>38900</v>
-      </c>
-      <c r="H17" s="3">
-        <v>33500</v>
-      </c>
-      <c r="I17" s="3">
-        <v>33700</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>19500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>16300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>64000</v>
+        <v>43500</v>
       </c>
       <c r="E18" s="3">
-        <v>62000</v>
+        <v>39500</v>
       </c>
       <c r="F18" s="3">
-        <v>63200</v>
+        <v>37200</v>
       </c>
       <c r="G18" s="3">
-        <v>61000</v>
+        <v>40200</v>
       </c>
       <c r="H18" s="3">
-        <v>58600</v>
+        <v>35300</v>
       </c>
       <c r="I18" s="3">
-        <v>53700</v>
+        <v>33600</v>
       </c>
       <c r="J18" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="K18" s="3">
         <v>66300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>54400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>54300</v>
-      </c>
-      <c r="M18" s="3">
-        <v>53500</v>
       </c>
       <c r="N18" s="3">
         <v>53500</v>
       </c>
       <c r="O18" s="3">
+        <v>53500</v>
+      </c>
+      <c r="P18" s="3">
         <v>35100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>35600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>33700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>34000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>32600</v>
       </c>
     </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1276,137 +1309,144 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-27300</v>
+        <v>2700</v>
       </c>
       <c r="E20" s="3">
-        <v>-27700</v>
+        <v>2800</v>
       </c>
       <c r="F20" s="3">
-        <v>-25800</v>
+        <v>2900</v>
       </c>
       <c r="G20" s="3">
+        <v>2800</v>
+      </c>
+      <c r="H20" s="3">
+        <v>3500</v>
+      </c>
+      <c r="I20" s="3">
+        <v>3100</v>
+      </c>
+      <c r="J20" s="3">
+        <v>2700</v>
+      </c>
+      <c r="K20" s="3">
         <v>-29200</v>
       </c>
-      <c r="H20" s="3">
-        <v>-28200</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-66700</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-29200</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-29500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-22400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-21600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-31700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-25000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-10600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-9500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-9800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>45200</v>
+      </c>
+      <c r="E21" s="3">
         <v>41200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>39100</v>
       </c>
-      <c r="F21" s="3">
-        <v>42700</v>
-      </c>
       <c r="G21" s="3">
+        <v>43500</v>
+      </c>
+      <c r="H21" s="3">
         <v>35700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>35600</v>
       </c>
-      <c r="I21" s="3">
-        <v>-8900</v>
-      </c>
       <c r="J21" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="K21" s="3">
         <v>42000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>30000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>37000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>38700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>26400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>14200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>27500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>26900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>27400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>27200</v>
       </c>
     </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1435,114 +1475,123 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>40800</v>
+      </c>
+      <c r="E23" s="3">
         <v>36700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>34300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>37400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>31800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>30500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-13100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>37100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>24800</v>
-      </c>
-      <c r="L23" s="3">
-        <v>31900</v>
       </c>
       <c r="M23" s="3">
         <v>31900</v>
       </c>
       <c r="N23" s="3">
+        <v>31900</v>
+      </c>
+      <c r="O23" s="3">
         <v>21800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>10100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>25000</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>24200</v>
       </c>
       <c r="R23" s="3">
         <v>24200</v>
       </c>
       <c r="S23" s="3">
+        <v>24200</v>
+      </c>
+      <c r="T23" s="3">
         <v>24600</v>
       </c>
     </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E24" s="3">
         <v>7500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>6500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>6800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>14700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>7900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-4200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>9500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>6300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>7900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>7700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>5500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>6700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>5900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>6100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>6400</v>
       </c>
     </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1594,114 +1643,123 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>32500</v>
+      </c>
+      <c r="E26" s="3">
         <v>29300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>27800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>30700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>17200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>22600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-8900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>27600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>18500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>24000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>24200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>16300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>7800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>18300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>18200</v>
-      </c>
-      <c r="R26" s="3">
-        <v>18100</v>
       </c>
       <c r="S26" s="3">
         <v>18100</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3">
+        <v>18100</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>32500</v>
+      </c>
+      <c r="E27" s="3">
         <v>29300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>27800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>30700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>17200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>22600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-8900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>27600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>18500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>24000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>24200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>16300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>7800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>18300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>18200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>18000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1753,8 +1811,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1806,8 +1867,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1859,8 +1923,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1912,114 +1979,123 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>27300</v>
+        <v>-2700</v>
       </c>
       <c r="E32" s="3">
-        <v>27700</v>
+        <v>-2800</v>
       </c>
       <c r="F32" s="3">
-        <v>25800</v>
+        <v>-2900</v>
       </c>
       <c r="G32" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="K32" s="3">
         <v>29200</v>
       </c>
-      <c r="H32" s="3">
-        <v>28200</v>
-      </c>
-      <c r="I32" s="3">
-        <v>66700</v>
-      </c>
-      <c r="J32" s="3">
-        <v>29200</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>29500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>22400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>21600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>31700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>25000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>10600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>9500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>9800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>8000</v>
       </c>
     </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>32500</v>
+      </c>
+      <c r="E33" s="3">
         <v>29300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>27800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>30700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>17200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>22600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-8900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>27600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>18500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>24000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>24200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>16300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>7800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>18300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>18200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>18000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2071,119 +2147,128 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>32500</v>
+      </c>
+      <c r="E35" s="3">
         <v>29300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>27800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>30700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>17200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>22600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-8900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>27600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>18500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>24000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>24200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>16300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>7800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>18300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>18200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>18000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2203,8 +2288,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2224,137 +2310,144 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>113600</v>
+        <v>428000</v>
       </c>
       <c r="E41" s="3">
-        <v>87300</v>
+        <v>408500</v>
       </c>
       <c r="F41" s="3">
-        <v>136300</v>
+        <v>427400</v>
       </c>
       <c r="G41" s="3">
-        <v>117000</v>
+        <v>491400</v>
       </c>
       <c r="H41" s="3">
-        <v>131800</v>
+        <v>545900</v>
       </c>
       <c r="I41" s="3">
-        <v>104800</v>
+        <v>505200</v>
       </c>
       <c r="J41" s="3">
+        <v>114200</v>
+      </c>
+      <c r="K41" s="3">
         <v>133700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>132000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>111700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>203400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>231300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>241700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>101000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>88600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>118000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>100900</v>
       </c>
     </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>359700</v>
+        <v>3200</v>
       </c>
       <c r="E42" s="3">
-        <v>406200</v>
+        <v>3900</v>
       </c>
       <c r="F42" s="3">
-        <v>419100</v>
+        <v>5600</v>
       </c>
       <c r="G42" s="3">
-        <v>494800</v>
+        <v>6400</v>
       </c>
       <c r="H42" s="3">
-        <v>440800</v>
+        <v>7600</v>
       </c>
       <c r="I42" s="3">
-        <v>78200</v>
+        <v>9800</v>
       </c>
       <c r="J42" s="3">
+        <v>11300</v>
+      </c>
+      <c r="K42" s="3">
         <v>98800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>399000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>138100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>266500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>430000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1171600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>748200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>702800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>742000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>812300</v>
       </c>
     </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2383,31 +2476,34 @@
       <c r="S43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="E44" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="F44" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="G44" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="H44" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I44" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="J44" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2436,31 +2532,34 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>30900</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>32700</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>50100</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>24200</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>24200</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>21500</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>21800</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -2489,31 +2588,34 @@
       <c r="S45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>474100</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>455700</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>489400</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>527500</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>586200</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>541900</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>154200</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2542,31 +2644,34 @@
       <c r="S46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>853100</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>827500</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>831600</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>827000</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>819100</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>946300</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>1048000</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2595,114 +2700,123 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>123600</v>
+      </c>
+      <c r="E48" s="3">
         <v>121000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>120000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>118800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>117700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>117300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>112600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>109000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>106600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>96700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>94300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>94600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>83500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>61600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>59400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>59900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>64200</v>
       </c>
     </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>400800</v>
+      </c>
+      <c r="E49" s="3">
         <v>402400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>404400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>406000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>408100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>410400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>412800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>415500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>426500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>350600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>351900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>353100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>283100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>185200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>185400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>185600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>185700</v>
       </c>
     </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2754,8 +2868,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2807,31 +2924,34 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>294600</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
+        <v>286700</v>
       </c>
       <c r="F52" s="3">
-        <v>0</v>
+        <v>268100</v>
       </c>
       <c r="G52" s="3">
-        <v>0</v>
+        <v>299100</v>
       </c>
       <c r="H52" s="3">
-        <v>0</v>
+        <v>308900</v>
       </c>
       <c r="I52" s="3">
-        <v>0</v>
+        <v>306900</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>303500</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -2860,8 +2980,11 @@
       <c r="S52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2913,61 +3036,67 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8637100</v>
+      </c>
+      <c r="E54" s="3">
         <v>8557000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8446700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8468700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8416200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8482600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8192400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8764000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8895900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7370300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7320200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7695000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6407800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4587300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4543800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4551800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>4706400</v>
       </c>
     </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2987,8 +3116,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3008,61 +3138,65 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>62100</v>
+        <v>7260000</v>
       </c>
       <c r="E57" s="3">
-        <v>55000</v>
+        <v>7241100</v>
       </c>
       <c r="F57" s="3">
-        <v>64900</v>
+        <v>7165700</v>
       </c>
       <c r="G57" s="3">
-        <v>61600</v>
+        <v>7197800</v>
       </c>
       <c r="H57" s="3">
-        <v>58800</v>
+        <v>7182400</v>
       </c>
       <c r="I57" s="3">
-        <v>54500</v>
+        <v>7198600</v>
       </c>
       <c r="J57" s="3">
+        <v>6928600</v>
+      </c>
+      <c r="K57" s="3">
         <v>70200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>56300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>47600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>45800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>68700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>58000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>43800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>49200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>48300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>48900</v>
       </c>
     </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3076,16 +3210,16 @@
         <v>0</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -3114,31 +3248,34 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>0</v>
-      </c>
-      <c r="E59" s="3">
-        <v>0</v>
-      </c>
-      <c r="F59" s="3">
-        <v>0</v>
-      </c>
-      <c r="G59" s="3">
-        <v>0</v>
-      </c>
-      <c r="H59" s="3">
-        <v>0</v>
-      </c>
-      <c r="I59" s="3">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3">
-        <v>0</v>
+      <c r="D59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K59" s="3">
         <v>0</v>
@@ -3167,31 +3304,34 @@
       <c r="S59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>7326600</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>7249900</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>7173500</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>7208100</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>7189400</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>7254900</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>6982800</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -3220,84 +3360,90 @@
       <c r="S60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>157400</v>
+        <v>161200</v>
       </c>
       <c r="E61" s="3">
-        <v>157300</v>
+        <v>162400</v>
       </c>
       <c r="F61" s="3">
-        <v>161900</v>
+        <v>162300</v>
       </c>
       <c r="G61" s="3">
-        <v>192800</v>
+        <v>175800</v>
       </c>
       <c r="H61" s="3">
-        <v>192600</v>
+        <v>197800</v>
       </c>
       <c r="I61" s="3">
-        <v>192400</v>
+        <v>197600</v>
       </c>
       <c r="J61" s="3">
+        <v>197400</v>
+      </c>
+      <c r="K61" s="3">
         <v>192300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>192200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>192000</v>
-      </c>
-      <c r="M61" s="3">
-        <v>191900</v>
       </c>
       <c r="N61" s="3">
         <v>191900</v>
       </c>
       <c r="O61" s="3">
+        <v>191900</v>
+      </c>
+      <c r="P61" s="3">
         <v>124200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>25100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>25000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>24900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>376800</v>
       </c>
     </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
+      <c r="D62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>53300</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>47300</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>45900</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>54500</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>52500</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>50300</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -3326,8 +3472,11 @@
       <c r="S62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3379,8 +3528,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3432,8 +3584,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3485,61 +3640,67 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7487800</v>
+      </c>
+      <c r="E66" s="3">
         <v>7465600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7383000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7429700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7441700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7505000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7230600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7791400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7957500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6530900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6483900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6803100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5678500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4028000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3993800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4012600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4168300</v>
       </c>
     </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3559,8 +3720,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3612,8 +3774,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3665,8 +3830,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3718,8 +3886,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3771,61 +3942,67 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>535600</v>
+      </c>
+      <c r="E72" s="3">
         <v>507400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>482300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>458300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>431300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>417900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>399000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>407900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>380300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>361800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>337800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>313600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>297300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>289500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>271200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>253000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>235000</v>
       </c>
     </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3877,8 +4054,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3930,8 +4110,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3983,61 +4166,67 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1149300</v>
+      </c>
+      <c r="E76" s="3">
         <v>1091400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1063700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1039000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>974500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>977600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>961800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>972500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>938500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>839400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>836300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>891900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>729300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>559400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>550000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>539200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>538100</v>
       </c>
     </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4089,119 +4278,128 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>32500</v>
+      </c>
+      <c r="E81" s="3">
         <v>29300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>27800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>30700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>17200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>22600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-8900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>27600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>18500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>24000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>24200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>16300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>7800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>18300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>18200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>18000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4221,61 +4419,65 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>4400</v>
+        <v>1900</v>
       </c>
       <c r="E83" s="3">
-        <v>4800</v>
+        <v>3000</v>
       </c>
       <c r="F83" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G83" s="3">
+        <v>100</v>
+      </c>
+      <c r="H83" s="3">
+        <v>3600</v>
+      </c>
+      <c r="I83" s="3">
+        <v>3700</v>
+      </c>
+      <c r="J83" s="3">
+        <v>5300</v>
+      </c>
+      <c r="K83" s="3">
+        <v>4900</v>
+      </c>
+      <c r="L83" s="3">
         <v>5200</v>
       </c>
-      <c r="G83" s="3">
-        <v>3900</v>
-      </c>
-      <c r="H83" s="3">
-        <v>5100</v>
-      </c>
-      <c r="I83" s="3">
-        <v>4200</v>
-      </c>
-      <c r="J83" s="3">
-        <v>4900</v>
-      </c>
-      <c r="K83" s="3">
-        <v>5200</v>
-      </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>6800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>3100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4327,8 +4529,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4380,8 +4585,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4433,8 +4641,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4486,8 +4697,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4539,61 +4753,67 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>39600</v>
+      </c>
+      <c r="E89" s="3">
         <v>37300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>23400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>37800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>21800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>32800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>15500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>30000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>38000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>27400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>21900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>45400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>9200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>4800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>38200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>14600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>44100</v>
       </c>
     </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4613,61 +4833,65 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-6900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5900</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-3200</v>
       </c>
       <c r="P91" s="3">
         <v>-3200</v>
       </c>
       <c r="Q91" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="R91" s="3">
         <v>-500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4719,8 +4943,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4772,61 +4999,67 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-41000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-127700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-49000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-78700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>88700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>92700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>488800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-134500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-169600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-283100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>70900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-637600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>324600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>24600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-82200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>109700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-19200</v>
       </c>
     </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4846,31 +5079,32 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-4200</v>
+        <v>4200</v>
       </c>
       <c r="E96" s="3">
-        <v>-3800</v>
+        <v>4200</v>
       </c>
       <c r="F96" s="3">
-        <v>-3700</v>
+        <v>3800</v>
       </c>
       <c r="G96" s="3">
-        <v>-3700</v>
+        <v>3700</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>3700</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+        <v>3700</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4899,8 +5133,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4952,8 +5189,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5005,8 +5245,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5058,84 +5301,90 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E100" s="3">
         <v>71500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-38400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-13500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-69900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>265500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-544900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-179100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>388900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>40800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-292200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-163100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>224300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>27200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-23100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-175000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -5164,57 +5413,63 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>19500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-18900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-64000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-54400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>40700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>391000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-40500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-283600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>257300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-214900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-199400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-755300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>558200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>56600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-67000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-50700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>30900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NIC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NIC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="92">
   <si>
     <t>NIC</t>
   </si>
@@ -656,151 +656,157 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>91400</v>
+      </c>
+      <c r="E8" s="3">
         <v>90000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>83600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>81500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>87700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>77600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>75400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>31800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>85800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>70700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>59500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>57900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>57600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>38700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>38300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>36900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>38000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>37300</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -855,35 +861,38 @@
       <c r="T9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>91400</v>
+      </c>
+      <c r="E10" s="3">
         <v>90000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>83600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>81500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>87700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>77600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>75400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>31800</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
@@ -911,8 +920,11 @@
       <c r="T10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -933,8 +945,9 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -989,8 +1002,11 @@
       <c r="T12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1045,8 +1061,11 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1059,21 +1078,21 @@
       <c r="F14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>200</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
@@ -1101,64 +1120,70 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>4400</v>
+        <v>5800</v>
       </c>
       <c r="E15" s="3">
         <v>4400</v>
       </c>
       <c r="F15" s="3">
+        <v>4400</v>
+      </c>
+      <c r="G15" s="3">
         <v>4800</v>
       </c>
-      <c r="G15" s="3">
-        <v>6100</v>
-      </c>
       <c r="H15" s="3">
+        <v>8300</v>
+      </c>
+      <c r="I15" s="3">
         <v>3900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>5100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-2200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-1600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-1300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-1400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-1100</v>
-      </c>
-      <c r="P15" s="3">
-        <v>-800</v>
       </c>
       <c r="Q15" s="3">
         <v>-800</v>
       </c>
       <c r="R15" s="3">
-        <v>-900</v>
+        <v>-800</v>
       </c>
       <c r="S15" s="3">
         <v>-900</v>
       </c>
       <c r="T15" s="3">
+        <v>-900</v>
+      </c>
+      <c r="U15" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1176,120 +1201,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>45600</v>
+      </c>
+      <c r="E17" s="3">
         <v>46500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>44100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>44300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>47500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>42300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>41800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>42000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>19500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>16300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>45800</v>
+      </c>
+      <c r="E18" s="3">
         <v>43500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>39500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>37200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>40200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>35300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>33600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-10200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>66300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>54400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>54300</v>
-      </c>
-      <c r="N18" s="3">
-        <v>53500</v>
       </c>
       <c r="O18" s="3">
         <v>53500</v>
       </c>
       <c r="P18" s="3">
+        <v>53500</v>
+      </c>
+      <c r="Q18" s="3">
         <v>35100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>35600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>33700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>34000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>32600</v>
       </c>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1310,120 +1342,127 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E20" s="3">
         <v>2700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>3500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>3100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-29200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-29500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-22400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-21600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-31700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-25000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-10600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-9500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-9800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>49000</v>
+      </c>
+      <c r="E21" s="3">
         <v>45200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>41200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>39100</v>
       </c>
-      <c r="G21" s="3">
-        <v>43500</v>
-      </c>
       <c r="H21" s="3">
+        <v>45700</v>
+      </c>
+      <c r="I21" s="3">
         <v>35700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>35600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-8700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>42000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>30000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>37000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>38700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>26400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>14200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>27500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>26900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>27400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>27200</v>
       </c>
     </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1448,8 +1487,8 @@
       <c r="J22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1478,120 +1517,129 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>43200</v>
+      </c>
+      <c r="E23" s="3">
         <v>40800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>36700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>34300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>37400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>31800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>30500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-13100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>37100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>24800</v>
-      </c>
-      <c r="M23" s="3">
-        <v>31900</v>
       </c>
       <c r="N23" s="3">
         <v>31900</v>
       </c>
       <c r="O23" s="3">
+        <v>31900</v>
+      </c>
+      <c r="P23" s="3">
         <v>21800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>10100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>25000</v>
-      </c>
-      <c r="R23" s="3">
-        <v>24200</v>
       </c>
       <c r="S23" s="3">
         <v>24200</v>
       </c>
       <c r="T23" s="3">
+        <v>24200</v>
+      </c>
+      <c r="U23" s="3">
         <v>24600</v>
       </c>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E24" s="3">
         <v>8300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>7500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>6500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>6800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>14700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>7900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-4200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>9500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>6300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>7900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>7700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>5500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>6700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>5900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>6100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>6400</v>
       </c>
     </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1646,120 +1694,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>34500</v>
+      </c>
+      <c r="E26" s="3">
         <v>32500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>29300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>27800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>30700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>17200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>22600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-8900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>27600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>18500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>24000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>24200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>16300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>7800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>18300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>18200</v>
-      </c>
-      <c r="S26" s="3">
-        <v>18100</v>
       </c>
       <c r="T26" s="3">
         <v>18100</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3">
+        <v>18100</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>34500</v>
+      </c>
+      <c r="E27" s="3">
         <v>32500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>29300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>27800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>30700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>17200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>22600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-8900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>27600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>18500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>24000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>24200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>16300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>7800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>18300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>18200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>18000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1814,8 +1871,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1870,8 +1930,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1926,8 +1989,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1982,120 +2048,129 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-3500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-3100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>29200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>29500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>22400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>21600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>31700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>25000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>10600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>9500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>9800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>8000</v>
       </c>
     </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>34500</v>
+      </c>
+      <c r="E33" s="3">
         <v>32500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>29300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>27800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>30700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>17200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>22600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-8900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>27600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>18500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>24000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>24200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>16300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>7800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>18300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>18200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>18000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2150,125 +2225,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>34500</v>
+      </c>
+      <c r="E35" s="3">
         <v>32500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>29300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>27800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>30700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>17200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>22600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-8900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>27600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>18500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>24000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>24200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>16300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>7800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>18300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>18200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>18000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2289,8 +2373,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2311,120 +2396,127 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>536000</v>
+      </c>
+      <c r="E41" s="3">
         <v>428000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>408500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>427400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>491400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>545900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>505200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>114200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>133700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>132000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>111700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>203400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>231300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>241700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>101000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>88600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>118000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>100900</v>
       </c>
     </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E42" s="3">
         <v>3200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>3900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>5600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>6400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>7600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>9800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>11300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>98800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>399000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>138100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>266500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>430000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1171600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>748200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>702800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>742000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>812300</v>
       </c>
     </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2449,8 +2541,8 @@
       <c r="J43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -2479,35 +2571,38 @@
       <c r="T43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>700</v>
+      </c>
+      <c r="E44" s="3">
         <v>900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2000</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
       <c r="L44" s="3">
         <v>0</v>
       </c>
@@ -2535,35 +2630,38 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E45" s="3">
         <v>30900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>32700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>50100</v>
-      </c>
-      <c r="G45" s="3">
-        <v>24200</v>
       </c>
       <c r="H45" s="3">
         <v>24200</v>
       </c>
       <c r="I45" s="3">
+        <v>24200</v>
+      </c>
+      <c r="J45" s="3">
         <v>21500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>21800</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
@@ -2591,35 +2689,38 @@
       <c r="T45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>570400</v>
+      </c>
+      <c r="E46" s="3">
         <v>474100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>455700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>489400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>527500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>586200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>541900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>154200</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -2647,35 +2748,38 @@
       <c r="T46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>834200</v>
+      </c>
+      <c r="E47" s="3">
         <v>853100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>827500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>831600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>827000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>819100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>946300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1048000</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
@@ -2703,120 +2807,129 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>127000</v>
+      </c>
+      <c r="E48" s="3">
         <v>123600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>121000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>120000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>118800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>117700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>117300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>112600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>109000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>106600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>96700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>94300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>94600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>83500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>61600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>59400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>59900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>64200</v>
       </c>
     </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>400100</v>
+      </c>
+      <c r="E49" s="3">
         <v>400800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>402400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>404400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>406000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>408100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>410400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>412800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>415500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>426500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>350600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>351900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>353100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>283100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>185200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>185400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>185600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>185700</v>
       </c>
     </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2871,8 +2984,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2927,35 +3043,38 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>304800</v>
+      </c>
+      <c r="E52" s="3">
         <v>294600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>286700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>268100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>299100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>308900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>306900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>303500</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
       <c r="L52" s="3">
         <v>0</v>
       </c>
@@ -2983,8 +3102,11 @@
       <c r="T52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3039,64 +3161,70 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8796800</v>
+      </c>
+      <c r="E54" s="3">
         <v>8637100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8557000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8446700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8468700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8416200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8482600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8192400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8764000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8895900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7370300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7320200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7695000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6407800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4587300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4543800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>4551800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>4706400</v>
       </c>
     </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3117,8 +3245,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3139,69 +3268,73 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7403700</v>
+      </c>
+      <c r="E57" s="3">
         <v>7260000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7241100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7165700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7197800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7182400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7198600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6928600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>70200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>56300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>47600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>45800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>68700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>58000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>43800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>49200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>48300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>48900</v>
       </c>
     </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
@@ -3210,19 +3343,19 @@
         <v>0</v>
       </c>
       <c r="G58" s="3">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
       </c>
       <c r="I58" s="3">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="J58" s="3">
         <v>50000</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -3251,8 +3384,11 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3277,8 +3413,8 @@
       <c r="J59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K59" s="3">
-        <v>0</v>
+      <c r="K59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L59" s="3">
         <v>0</v>
@@ -3307,35 +3443,38 @@
       <c r="T59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7413700</v>
+      </c>
+      <c r="E60" s="3">
         <v>7326600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7249900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7173500</v>
       </c>
-      <c r="G60" s="3">
-        <v>7208100</v>
-      </c>
       <c r="H60" s="3">
+        <v>7205600</v>
+      </c>
+      <c r="I60" s="3">
         <v>7189400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7254900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6982800</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -3363,91 +3502,97 @@
       <c r="T60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>168100</v>
+      </c>
+      <c r="E61" s="3">
         <v>161200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>162400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>162300</v>
       </c>
-      <c r="G61" s="3">
-        <v>175800</v>
-      </c>
       <c r="H61" s="3">
+        <v>166900</v>
+      </c>
+      <c r="I61" s="3">
         <v>197800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>197600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>197400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>192300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>192200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>192000</v>
-      </c>
-      <c r="N61" s="3">
-        <v>191900</v>
       </c>
       <c r="O61" s="3">
         <v>191900</v>
       </c>
       <c r="P61" s="3">
+        <v>191900</v>
+      </c>
+      <c r="Q61" s="3">
         <v>124200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>25100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>25000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>24900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>376800</v>
       </c>
     </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E62" s="3">
+      <c r="D62" s="3">
+        <v>42200</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F62" s="3">
         <v>53300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>47300</v>
       </c>
-      <c r="G62" s="3">
-        <v>45900</v>
-      </c>
       <c r="H62" s="3">
+        <v>57200</v>
+      </c>
+      <c r="I62" s="3">
         <v>54500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>52500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>50300</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
@@ -3475,8 +3620,11 @@
       <c r="T62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3531,8 +3679,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3587,8 +3738,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3643,64 +3797,70 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7623900</v>
+      </c>
+      <c r="E66" s="3">
         <v>7487800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7465600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7383000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7429700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7441700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7505000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7230600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7791400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7957500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6530900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6483900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>6803100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5678500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4028000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3993800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4012600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4168300</v>
       </c>
     </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3721,8 +3881,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3777,8 +3938,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3833,8 +3997,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3889,8 +4056,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3945,64 +4115,70 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>565800</v>
+      </c>
+      <c r="E72" s="3">
         <v>535600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>507400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>482300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>458300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>431300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>417900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>399000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>407900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>380300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>361800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>337800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>313600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>297300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>289500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>271200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>253000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>235000</v>
       </c>
     </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4057,8 +4233,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4113,8 +4292,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4169,64 +4351,70 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1172900</v>
+      </c>
+      <c r="E76" s="3">
         <v>1149300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1091400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1063700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1039000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>974500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>977600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>961800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>972500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>938500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>839400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>836300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>891900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>729300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>559400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>550000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>539200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>538100</v>
       </c>
     </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4281,125 +4469,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>34500</v>
+      </c>
+      <c r="E81" s="3">
         <v>32500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>29300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>27800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>30700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>17200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>22600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-8900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>27600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>18500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>24000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>24200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>16300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>7800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>18300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>18200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>18000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4420,64 +4617,68 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E83" s="3">
         <v>1900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>5300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>5000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>6800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>2700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>3100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4532,8 +4733,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4588,8 +4792,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4644,8 +4851,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4700,8 +4910,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4756,64 +4969,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>33400</v>
+      </c>
+      <c r="E89" s="3">
         <v>39600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>37300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>23400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>37800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>21800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>32800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>15500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>30000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>38000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>27400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>21900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>45400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>9200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>4800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>38200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>14600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>44100</v>
       </c>
     </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4834,64 +5053,68 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-6900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5900</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-3200</v>
       </c>
       <c r="Q91" s="3">
         <v>-3200</v>
       </c>
       <c r="R91" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="S91" s="3">
         <v>-500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4946,8 +5169,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5002,64 +5228,70 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-70800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-41000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-127700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-49000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-78700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>88700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>92700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>488800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-134500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-169600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-283100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>70900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-637600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>324600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>24600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-82200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>109700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-19200</v>
       </c>
     </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5080,22 +5312,23 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>4200</v>
+        <v>4300</v>
       </c>
       <c r="E96" s="3">
         <v>4200</v>
       </c>
       <c r="F96" s="3">
+        <v>4200</v>
+      </c>
+      <c r="G96" s="3">
         <v>3800</v>
-      </c>
-      <c r="G96" s="3">
-        <v>3700</v>
       </c>
       <c r="H96" s="3">
         <v>3700</v>
@@ -5103,11 +5336,11 @@
       <c r="I96" s="3">
         <v>3700</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="J96" s="3">
+        <v>3700</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -5136,8 +5369,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5192,8 +5428,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5248,8 +5487,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5304,64 +5546,70 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>145400</v>
+      </c>
+      <c r="E100" s="3">
         <v>20800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>71500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-38400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-13500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-69900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>265500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-544900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-179100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>388900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>40800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-292200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-163100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>224300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>27200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-23100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-175000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5386,8 +5634,8 @@
       <c r="J101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -5416,60 +5664,66 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>108100</v>
+      </c>
+      <c r="E102" s="3">
         <v>19500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-18900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-64000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-54400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>40700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>391000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-40500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-283600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>257300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-214900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-199400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-755300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>558200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>56600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-67000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-50700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>30900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NIC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NIC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="92">
   <si>
     <t>NIC</t>
   </si>
@@ -656,157 +656,164 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>87900</v>
+      </c>
+      <c r="E8" s="3">
         <v>91400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>90000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>83600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>81500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>87700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>77600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>75400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>31800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>85800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>70700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>59500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>57900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>57600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>38700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>38300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>36900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>38000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>37300</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -864,38 +871,41 @@
       <c r="U9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>87900</v>
+      </c>
+      <c r="E10" s="3">
         <v>91400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>90000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>83600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>81500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>87700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>77600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>75400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>31800</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
@@ -923,8 +933,11 @@
       <c r="U10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -946,8 +959,9 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1005,8 +1019,11 @@
       <c r="U12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1064,8 +1081,11 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1081,21 +1101,21 @@
       <c r="G14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>200</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
@@ -1123,67 +1143,73 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E15" s="3">
         <v>5800</v>
-      </c>
-      <c r="E15" s="3">
-        <v>4400</v>
       </c>
       <c r="F15" s="3">
         <v>4400</v>
       </c>
       <c r="G15" s="3">
+        <v>4400</v>
+      </c>
+      <c r="H15" s="3">
         <v>4800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>8300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>3900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>5100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-2200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-1600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-1300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-1400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-1100</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>-800</v>
       </c>
       <c r="R15" s="3">
         <v>-800</v>
       </c>
       <c r="S15" s="3">
-        <v>-900</v>
+        <v>-800</v>
       </c>
       <c r="T15" s="3">
         <v>-900</v>
       </c>
       <c r="U15" s="3">
+        <v>-900</v>
+      </c>
+      <c r="V15" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1202,126 +1228,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>45300</v>
+      </c>
+      <c r="E17" s="3">
         <v>45600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>46500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>44100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>44300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>47500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>42300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>41800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>42000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>19500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>16300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>42600</v>
+      </c>
+      <c r="E18" s="3">
         <v>45800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>43500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>39500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>37200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>40200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>35300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>33600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-10200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>66300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>54400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>54300</v>
-      </c>
-      <c r="O18" s="3">
-        <v>53500</v>
       </c>
       <c r="P18" s="3">
         <v>53500</v>
       </c>
       <c r="Q18" s="3">
+        <v>53500</v>
+      </c>
+      <c r="R18" s="3">
         <v>35100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>35600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>33700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>34000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>32600</v>
       </c>
     </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1343,126 +1376,133 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E20" s="3">
         <v>2600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>3500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>3100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-29200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-29500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-22400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-21600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-31700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-25000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-10600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-9500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-9800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>44000</v>
+      </c>
+      <c r="E21" s="3">
         <v>49000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>45200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>41200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>39100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>45700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>35700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>35600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-8700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>42000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>30000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>37000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>38700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>26400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>14200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>27500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>26900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>27400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>27200</v>
       </c>
     </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1490,8 +1530,8 @@
       <c r="K22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1520,126 +1560,135 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>40100</v>
+      </c>
+      <c r="E23" s="3">
         <v>43200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>40800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>36700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>34300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>37400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>31800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>30500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-13100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>37100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>24800</v>
-      </c>
-      <c r="N23" s="3">
-        <v>31900</v>
       </c>
       <c r="O23" s="3">
         <v>31900</v>
       </c>
       <c r="P23" s="3">
+        <v>31900</v>
+      </c>
+      <c r="Q23" s="3">
         <v>21800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>10100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>25000</v>
-      </c>
-      <c r="S23" s="3">
-        <v>24200</v>
       </c>
       <c r="T23" s="3">
         <v>24200</v>
       </c>
       <c r="U23" s="3">
+        <v>24200</v>
+      </c>
+      <c r="V23" s="3">
         <v>24600</v>
       </c>
     </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E24" s="3">
         <v>8700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>8300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>7500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>6500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>6800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>14700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>7900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-4200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>9500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>6300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>7900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>7700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>5500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>6700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>5900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>6100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>6400</v>
       </c>
     </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1697,126 +1746,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>32600</v>
+      </c>
+      <c r="E26" s="3">
         <v>34500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>32500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>29300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>27800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>30700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>17200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>22600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-8900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>27600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>18500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>24000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>24200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>16300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>7800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>18300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>18200</v>
-      </c>
-      <c r="T26" s="3">
-        <v>18100</v>
       </c>
       <c r="U26" s="3">
         <v>18100</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3">
+        <v>18100</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>32600</v>
+      </c>
+      <c r="E27" s="3">
         <v>34500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>32500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>29300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>27800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>30700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>17200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>22600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-8900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>27600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>18500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>24000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>24200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>16300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>7800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>18300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>18200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>18000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1874,8 +1932,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1933,8 +1994,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1992,8 +2056,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2051,126 +2118,135 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-3500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-3100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>29200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>29500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>22400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>21600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>31700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>25000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>10600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>9500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>9800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>8000</v>
       </c>
     </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>32600</v>
+      </c>
+      <c r="E33" s="3">
         <v>34500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>32500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>29300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>27800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>30700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>17200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>22600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-8900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>27600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>18500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>24000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>24200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>16300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>7800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>18300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>18200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>18000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2228,131 +2304,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>32600</v>
+      </c>
+      <c r="E35" s="3">
         <v>34500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>32500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>29300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>27800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>30700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>17200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>22600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-8900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>27600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>18500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>24000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>24200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>16300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>7800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>18300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>18200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>18000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2374,8 +2459,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2397,126 +2483,133 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>572200</v>
+      </c>
+      <c r="E41" s="3">
         <v>536000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>428000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>408500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>427400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>491400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>545900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>505200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>114200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>133700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>132000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>111700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>203400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>231300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>241700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>101000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>88600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>118000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>100900</v>
       </c>
     </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>1000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>3200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>3900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>5600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>6400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>7600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>9800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>11300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>98800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>399000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>138100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>266500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>430000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1171600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>748200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>702800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>742000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>812300</v>
       </c>
     </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2544,8 +2637,8 @@
       <c r="K43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -2574,38 +2667,41 @@
       <c r="U43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>900</v>
+      </c>
+      <c r="E44" s="3">
         <v>700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2000</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
       <c r="M44" s="3">
         <v>0</v>
       </c>
@@ -2633,38 +2729,41 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>26200</v>
+      </c>
+      <c r="E45" s="3">
         <v>25000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>30900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>32700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>50100</v>
-      </c>
-      <c r="H45" s="3">
-        <v>24200</v>
       </c>
       <c r="I45" s="3">
         <v>24200</v>
       </c>
       <c r="J45" s="3">
+        <v>24200</v>
+      </c>
+      <c r="K45" s="3">
         <v>21500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>21800</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -2692,38 +2791,41 @@
       <c r="U45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>607400</v>
+      </c>
+      <c r="E46" s="3">
         <v>570400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>474100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>455700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>489400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>527500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>586200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>541900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>154200</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -2751,38 +2853,41 @@
       <c r="U46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>863400</v>
+      </c>
+      <c r="E47" s="3">
         <v>834200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>853100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>827500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>831600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>827000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>819100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>946300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1048000</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
@@ -2810,126 +2915,135 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>125300</v>
+      </c>
+      <c r="E48" s="3">
         <v>127000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>123600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>121000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>120000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>118800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>117700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>117300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>112600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>109000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>106600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>96700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>94300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>94600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>83500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>61600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>59400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>59900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>64200</v>
       </c>
     </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>398500</v>
+      </c>
+      <c r="E49" s="3">
         <v>400100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>400800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>402400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>404400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>406000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>408100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>410400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>412800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>415500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>426500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>350600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>351900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>353100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>283100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>185200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>185400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>185600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>185700</v>
       </c>
     </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2987,8 +3101,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3046,38 +3163,41 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>302600</v>
+      </c>
+      <c r="E52" s="3">
         <v>304800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>294600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>286700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>268100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>299100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>308900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>306900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>303500</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
       <c r="M52" s="3">
         <v>0</v>
       </c>
@@ -3105,8 +3225,11 @@
       <c r="U52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3164,67 +3287,73 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8975200</v>
+      </c>
+      <c r="E54" s="3">
         <v>8796800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8637100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8557000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8446700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8468700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8416200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8482600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8192400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8764000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8895900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7370300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7320200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7695000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6407800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4587300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>4543800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>4551800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>4706400</v>
       </c>
     </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3246,8 +3375,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3269,76 +3399,80 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7572200</v>
+      </c>
+      <c r="E57" s="3">
         <v>7403700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7260000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7241100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7165700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7197800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7182400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7198600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6928600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>70200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>56300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>47600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>45800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>68700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>58000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>43800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>49200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>48300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>48900</v>
       </c>
     </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>2200</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
       <c r="F58" s="3">
         <v>0</v>
       </c>
@@ -3352,13 +3486,13 @@
         <v>0</v>
       </c>
       <c r="J58" s="3">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="K58" s="3">
         <v>50000</v>
       </c>
       <c r="L58" s="3">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -3387,8 +3521,11 @@
       <c r="U58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3416,8 +3553,8 @@
       <c r="K59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L59" s="3">
-        <v>0</v>
+      <c r="L59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M59" s="3">
         <v>0</v>
@@ -3446,38 +3583,41 @@
       <c r="U59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7580200</v>
+      </c>
+      <c r="E60" s="3">
         <v>7413700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7326600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7249900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>7173500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7205600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7189400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7254900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6982800</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -3505,97 +3645,103 @@
       <c r="U60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>156600</v>
+      </c>
+      <c r="E61" s="3">
         <v>168100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>161200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>162400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>162300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>166900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>197800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>197600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>197400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>192300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>192200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>192000</v>
-      </c>
-      <c r="O61" s="3">
-        <v>191900</v>
       </c>
       <c r="P61" s="3">
         <v>191900</v>
       </c>
       <c r="Q61" s="3">
+        <v>191900</v>
+      </c>
+      <c r="R61" s="3">
         <v>124200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>25100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>25000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>24900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>376800</v>
       </c>
     </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>55200</v>
+      </c>
+      <c r="E62" s="3">
         <v>42200</v>
       </c>
-      <c r="E62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F62" s="3">
+      <c r="F62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G62" s="3">
         <v>53300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>47300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>57200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>54500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>52500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>50300</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
@@ -3623,8 +3769,11 @@
       <c r="U62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3682,8 +3831,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3741,8 +3893,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3800,67 +3955,73 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7792000</v>
+      </c>
+      <c r="E66" s="3">
         <v>7623900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7487800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7465600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7383000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7429700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7441700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7505000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7230600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7791400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>7957500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6530900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>6483900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>6803100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5678500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4028000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3993800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4012600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4168300</v>
       </c>
     </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3882,8 +4043,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3941,8 +4103,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4000,8 +4165,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4059,8 +4227,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4118,67 +4289,73 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>594100</v>
+      </c>
+      <c r="E72" s="3">
         <v>565800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>535600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>507400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>482300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>458300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>431300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>417900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>399000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>407900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>380300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>361800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>337800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>313600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>297300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>289500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>271200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>253000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>235000</v>
       </c>
     </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4236,8 +4413,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4295,8 +4475,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4354,67 +4537,73 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1183300</v>
+      </c>
+      <c r="E76" s="3">
         <v>1172900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1149300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1091400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1063700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1039000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>974500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>977600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>961800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>972500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>938500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>839400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>836300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>891900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>729300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>559400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>550000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>539200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>538100</v>
       </c>
     </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4472,131 +4661,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>32600</v>
+      </c>
+      <c r="E81" s="3">
         <v>34500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>32500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>29300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>27800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>30700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>17200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>22600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-8900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>27600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>18500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>24000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>24200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>16300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>7800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>18300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>18200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>18000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4618,67 +4816,71 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E83" s="3">
         <v>1300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>5200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>5000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>6800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>2500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>2700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>3100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4736,8 +4938,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4795,8 +5000,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4854,8 +5062,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4913,8 +5124,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4972,67 +5186,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>41800</v>
+      </c>
+      <c r="E89" s="3">
         <v>33400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>39600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>37300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>23400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>37800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>21800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>32800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>15500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>30000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>38000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>27400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>21900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>45400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>9200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>4800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>38200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>14600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>44100</v>
       </c>
     </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5054,67 +5274,71 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-5300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-6900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5900</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-3200</v>
       </c>
       <c r="R91" s="3">
         <v>-3200</v>
       </c>
       <c r="S91" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="T91" s="3">
         <v>-500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5172,8 +5396,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5231,67 +5458,73 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-138200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-70800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-41000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-127700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-49000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-78700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>88700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>92700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>488800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-134500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-169600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-283100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>70900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-637600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>324600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>24600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-82200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>109700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-19200</v>
       </c>
     </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5313,8 +5546,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5322,16 +5556,16 @@
         <v>4300</v>
       </c>
       <c r="E96" s="3">
-        <v>4200</v>
+        <v>4300</v>
       </c>
       <c r="F96" s="3">
         <v>4200</v>
       </c>
       <c r="G96" s="3">
+        <v>4200</v>
+      </c>
+      <c r="H96" s="3">
         <v>3800</v>
-      </c>
-      <c r="H96" s="3">
-        <v>3700</v>
       </c>
       <c r="I96" s="3">
         <v>3700</v>
@@ -5339,11 +5573,11 @@
       <c r="J96" s="3">
         <v>3700</v>
       </c>
-      <c r="K96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3">
+        <v>3700</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -5372,8 +5606,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5431,8 +5668,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5490,8 +5730,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5549,67 +5792,73 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>132500</v>
+      </c>
+      <c r="E100" s="3">
         <v>145400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>20800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>71500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-38400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-13500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-69900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>265500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-544900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-179100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>388900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>40800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-292200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-163100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>224300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>27200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-23100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-175000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5637,8 +5886,8 @@
       <c r="K101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -5667,63 +5916,69 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>36100</v>
+      </c>
+      <c r="E102" s="3">
         <v>108100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>19500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-18900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-64000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-54400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>40700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>391000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-40500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-283600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>257300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-214900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-199400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-755300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>558200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>56600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-67000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-50700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>30900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NIC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NIC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="92">
   <si>
     <t>NIC</t>
   </si>
@@ -656,164 +656,171 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>94700</v>
+      </c>
+      <c r="E8" s="3">
         <v>87900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>91400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>90000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>83600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>81500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>87700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>77600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>75400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>31800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>85800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>70700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>59500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>57900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>57600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>38700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>38300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>36900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>38000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>37300</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -874,41 +881,44 @@
       <c r="V9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>94700</v>
+      </c>
+      <c r="E10" s="3">
         <v>87900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>91400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>90000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>83600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>81500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>87700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>77600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>75400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>31800</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>5</v>
       </c>
@@ -936,8 +946,11 @@
       <c r="V10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -960,8 +973,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1022,8 +1036,11 @@
       <c r="V12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1084,8 +1101,11 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1104,21 +1124,21 @@
       <c r="H14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>200</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
@@ -1146,70 +1166,76 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E15" s="3">
         <v>3900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>5800</v>
-      </c>
-      <c r="F15" s="3">
-        <v>4400</v>
       </c>
       <c r="G15" s="3">
         <v>4400</v>
       </c>
       <c r="H15" s="3">
+        <v>4400</v>
+      </c>
+      <c r="I15" s="3">
         <v>4800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>8300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>5100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>4200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-2200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-1600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-1300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-1100</v>
-      </c>
-      <c r="R15" s="3">
-        <v>-800</v>
       </c>
       <c r="S15" s="3">
         <v>-800</v>
       </c>
       <c r="T15" s="3">
-        <v>-900</v>
+        <v>-800</v>
       </c>
       <c r="U15" s="3">
         <v>-900</v>
       </c>
       <c r="V15" s="3">
+        <v>-900</v>
+      </c>
+      <c r="W15" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1229,132 +1255,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>47400</v>
+      </c>
+      <c r="E17" s="3">
         <v>45300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>45600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>46500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>44100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>44300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>47500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>42300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>41800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>42000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>19500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>16300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>47300</v>
+      </c>
+      <c r="E18" s="3">
         <v>42600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>45800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>43500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>39500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>37200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>40200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>35300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>33600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-10200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>66300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>54400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>54300</v>
-      </c>
-      <c r="P18" s="3">
-        <v>53500</v>
       </c>
       <c r="Q18" s="3">
         <v>53500</v>
       </c>
       <c r="R18" s="3">
+        <v>53500</v>
+      </c>
+      <c r="S18" s="3">
         <v>35100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>35600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>33700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>34000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>32600</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1377,8 +1410,9 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1386,123 +1420,129 @@
         <v>2500</v>
       </c>
       <c r="E20" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F20" s="3">
         <v>2600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>3500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>3100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-29200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-29500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-22400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-21600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-31700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-25000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-10600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-9500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-9800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>48300</v>
+      </c>
+      <c r="E21" s="3">
         <v>44000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>49000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>45200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>41200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>39100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>45700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>35700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>35600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-8700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>42000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>30000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>37000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>38700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>26400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>14200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>27500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>26900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>27400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>27200</v>
       </c>
     </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1533,8 +1573,8 @@
       <c r="L22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1563,132 +1603,141 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>44800</v>
+      </c>
+      <c r="E23" s="3">
         <v>40100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>43200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>40800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>36700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>34300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>37400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>31800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>30500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-13100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>37100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>24800</v>
-      </c>
-      <c r="O23" s="3">
-        <v>31900</v>
       </c>
       <c r="P23" s="3">
         <v>31900</v>
       </c>
       <c r="Q23" s="3">
+        <v>31900</v>
+      </c>
+      <c r="R23" s="3">
         <v>21800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>10100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>25000</v>
-      </c>
-      <c r="T23" s="3">
-        <v>24200</v>
       </c>
       <c r="U23" s="3">
         <v>24200</v>
       </c>
       <c r="V23" s="3">
+        <v>24200</v>
+      </c>
+      <c r="W23" s="3">
         <v>24600</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E24" s="3">
         <v>7600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>8700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>8300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>7500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>6500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>6800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>14700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>7900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-4200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>9500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>6300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>7900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>7700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>5500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>6700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>5900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>6100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>6400</v>
       </c>
     </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1749,132 +1798,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>36000</v>
+      </c>
+      <c r="E26" s="3">
         <v>32600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>34500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>32500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>29300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>27800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>30700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>17200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>22600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-8900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>27600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>18500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>24000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>24200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>16300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>7800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>18300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>18200</v>
-      </c>
-      <c r="U26" s="3">
-        <v>18100</v>
       </c>
       <c r="V26" s="3">
         <v>18100</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3">
+        <v>18100</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>36000</v>
+      </c>
+      <c r="E27" s="3">
         <v>32600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>34500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>32500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>29300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>27800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>30700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>17200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>22600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-8900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>27600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>18500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>24000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>24200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>16300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>7800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>18300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>18200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>18000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1935,8 +1993,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1997,8 +2058,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2059,8 +2123,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2121,8 +2188,11 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2130,123 +2200,129 @@
         <v>-2500</v>
       </c>
       <c r="E32" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="F32" s="3">
         <v>-2600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-3500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-3100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>29200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>29500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>22400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>21600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>31700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>25000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>10600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>9500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>9800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>8000</v>
       </c>
     </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>36000</v>
+      </c>
+      <c r="E33" s="3">
         <v>32600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>34500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>32500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>29300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>27800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>30700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>17200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>22600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-8900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>27600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>18500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>24000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>24200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>16300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>7800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>18300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>18200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>18000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2307,137 +2383,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>36000</v>
+      </c>
+      <c r="E35" s="3">
         <v>32600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>34500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>32500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>29300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>27800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>30700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>17200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>22600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-8900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>27600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>18500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>24000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>24200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>16300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>7800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>18300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>18200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>18000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2460,8 +2545,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2484,70 +2570,74 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>422600</v>
+      </c>
+      <c r="E41" s="3">
         <v>572200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>536000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>428000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>408500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>427400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>491400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>545900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>505200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>114200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>133700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>132000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>111700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>203400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>231300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>241700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>101000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>88600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>118000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>100900</v>
       </c>
     </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2555,61 +2645,64 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>1000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>3200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>5600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>6400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>7600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>9800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>11300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>98800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>399000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>138100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>266500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>430000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>1171600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>748200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>702800</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>742000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>812300</v>
       </c>
     </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2640,8 +2733,8 @@
       <c r="L43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -2670,8 +2763,11 @@
       <c r="V43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2679,32 +2775,32 @@
         <v>900</v>
       </c>
       <c r="E44" s="3">
+        <v>900</v>
+      </c>
+      <c r="F44" s="3">
         <v>700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2000</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
-      </c>
       <c r="N44" s="3">
         <v>0</v>
       </c>
@@ -2732,41 +2828,44 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>26800</v>
+      </c>
+      <c r="E45" s="3">
         <v>26200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>25000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>30900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>32700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>50100</v>
-      </c>
-      <c r="I45" s="3">
-        <v>24200</v>
       </c>
       <c r="J45" s="3">
         <v>24200</v>
       </c>
       <c r="K45" s="3">
+        <v>24200</v>
+      </c>
+      <c r="L45" s="3">
         <v>21500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>21800</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
-      </c>
       <c r="N45" s="3">
         <v>0</v>
       </c>
@@ -2794,41 +2893,44 @@
       <c r="V45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>460300</v>
+      </c>
+      <c r="E46" s="3">
         <v>607400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>570400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>474100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>455700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>489400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>527500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>586200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>541900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>154200</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
@@ -2856,41 +2958,44 @@
       <c r="V46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>875400</v>
+      </c>
+      <c r="E47" s="3">
         <v>863400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>834200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>853100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>827500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>831600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>827000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>819100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>946300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1048000</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
       <c r="N47" s="3">
         <v>0</v>
       </c>
@@ -2918,132 +3023,141 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>123700</v>
+      </c>
+      <c r="E48" s="3">
         <v>125300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>127000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>123600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>121000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>120000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>118800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>117700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>117300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>112600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>109000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>106600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>96700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>94300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>94600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>83500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>61600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>59400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>59900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>64200</v>
       </c>
     </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>409100</v>
+      </c>
+      <c r="E49" s="3">
         <v>398500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>400100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>400800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>402400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>404400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>406000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>408100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>410400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>412800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>415500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>426500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>350600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>351900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>353100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>283100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>185200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>185400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>185600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>185700</v>
       </c>
     </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3104,8 +3218,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3166,41 +3283,44 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>291600</v>
+      </c>
+      <c r="E52" s="3">
         <v>302600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>304800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>294600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>286700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>268100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>299100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>308900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>306900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>303500</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
       <c r="N52" s="3">
         <v>0</v>
       </c>
@@ -3228,8 +3348,11 @@
       <c r="V52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3290,70 +3413,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8930800</v>
+      </c>
+      <c r="E54" s="3">
         <v>8975200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8796800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8637100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8557000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8446700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8468700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8416200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8482600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8192400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8764000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8895900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7370300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7320200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7695000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6407800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>4587300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>4543800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>4551800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>4706400</v>
       </c>
     </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3376,8 +3505,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3400,70 +3530,74 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7541700</v>
+      </c>
+      <c r="E57" s="3">
         <v>7572200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7403700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7260000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7241100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7165700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7197800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7182400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7198600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6928600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>70200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>56300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>47600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>45800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>68700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>58000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>43800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>49200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>48300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>48900</v>
       </c>
     </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3471,11 +3605,11 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>2200</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
         <v>0</v>
       </c>
@@ -3489,13 +3623,13 @@
         <v>0</v>
       </c>
       <c r="K58" s="3">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="L58" s="3">
         <v>50000</v>
       </c>
       <c r="M58" s="3">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -3524,8 +3658,11 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3556,8 +3693,8 @@
       <c r="L59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M59" s="3">
-        <v>0</v>
+      <c r="M59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N59" s="3">
         <v>0</v>
@@ -3586,41 +3723,44 @@
       <c r="V59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7550500</v>
+      </c>
+      <c r="E60" s="3">
         <v>7580200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7413700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7326600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>7249900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7173500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7205600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7189400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7254900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6982800</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
@@ -3648,103 +3788,109 @@
       <c r="V60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>134300</v>
+      </c>
+      <c r="E61" s="3">
         <v>156600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>168100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>161200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>162400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>162300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>166900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>197800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>197600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>197400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>192300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>192200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>192000</v>
-      </c>
-      <c r="P61" s="3">
-        <v>191900</v>
       </c>
       <c r="Q61" s="3">
         <v>191900</v>
       </c>
       <c r="R61" s="3">
+        <v>191900</v>
+      </c>
+      <c r="S61" s="3">
         <v>124200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>25100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>25000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>24900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>376800</v>
       </c>
     </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>55900</v>
+      </c>
+      <c r="E62" s="3">
         <v>55200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>42200</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G62" s="3">
+      <c r="G62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H62" s="3">
         <v>53300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>47300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>57200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>54500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>52500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>50300</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
       <c r="N62" s="3">
         <v>0</v>
       </c>
@@ -3772,8 +3918,11 @@
       <c r="V62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3834,8 +3983,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3896,8 +4048,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3958,70 +4113,76 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7740700</v>
+      </c>
+      <c r="E66" s="3">
         <v>7792000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7623900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7487800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7465600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7383000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7429700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7441700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7505000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7230600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>7791400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>7957500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>6530900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>6483900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>6803100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5678500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4028000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3993800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4012600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4168300</v>
       </c>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4044,8 +4205,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4106,8 +4268,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4168,8 +4333,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4230,8 +4398,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4292,70 +4463,76 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>625200</v>
+      </c>
+      <c r="E72" s="3">
         <v>594100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>565800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>535600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>507400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>482300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>458300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>431300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>417900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>399000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>407900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>380300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>361800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>337800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>313600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>297300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>289500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>271200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>253000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>235000</v>
       </c>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4416,8 +4593,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4478,8 +4658,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4540,70 +4723,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1190100</v>
+      </c>
+      <c r="E76" s="3">
         <v>1183300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1172900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1149300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1091400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1063700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1039000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>974500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>977600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>961800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>972500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>938500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>839400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>836300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>891900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>729300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>559400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>550000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>539200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>538100</v>
       </c>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4664,137 +4853,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>36000</v>
+      </c>
+      <c r="E81" s="3">
         <v>32600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>34500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>32500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>29300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>27800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>30700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>17200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>22600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-8900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>27600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>18500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>24000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>24200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>16300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>7800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>18300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>18200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>18000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4817,70 +5015,74 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E83" s="3">
         <v>3000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>5200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>6800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>4100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>2500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>2700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>3100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4941,8 +5143,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5003,8 +5208,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5065,8 +5273,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5127,8 +5338,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5189,70 +5403,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>38900</v>
+      </c>
+      <c r="E89" s="3">
         <v>41800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>33400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>39600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>37300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>23400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>37800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>21800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>32800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>15500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>30000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>38000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>27400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>21900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>45400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>9200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>4800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>38200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>14600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>44100</v>
       </c>
     </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5275,8 +5495,9 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5284,61 +5505,64 @@
         <v>-500</v>
       </c>
       <c r="E91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F91" s="3">
         <v>-5300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-6900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-5900</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-3200</v>
       </c>
       <c r="S91" s="3">
         <v>-3200</v>
       </c>
       <c r="T91" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="U91" s="3">
         <v>-500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5399,8 +5623,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5461,70 +5688,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-99800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-138200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-70800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-41000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-127700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-49000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-78700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>88700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>92700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>488800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-134500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-169600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-283100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>70900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-637600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>324600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>24600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-82200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>109700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-19200</v>
       </c>
     </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5547,28 +5780,29 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>4300</v>
+        <v>4900</v>
       </c>
       <c r="E96" s="3">
         <v>4300</v>
       </c>
       <c r="F96" s="3">
-        <v>4200</v>
+        <v>4300</v>
       </c>
       <c r="G96" s="3">
         <v>4200</v>
       </c>
       <c r="H96" s="3">
+        <v>4200</v>
+      </c>
+      <c r="I96" s="3">
         <v>3800</v>
-      </c>
-      <c r="I96" s="3">
-        <v>3700</v>
       </c>
       <c r="J96" s="3">
         <v>3700</v>
@@ -5576,11 +5810,11 @@
       <c r="K96" s="3">
         <v>3700</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="L96" s="3">
+        <v>3700</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -5609,8 +5843,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5671,8 +5908,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5733,8 +5973,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5795,70 +6038,76 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-88600</v>
+      </c>
+      <c r="E100" s="3">
         <v>132500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>145400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>20800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>71500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-38400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-13500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-69900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>265500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-544900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-179100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>388900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>40800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-292200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-163100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>224300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>27200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-23100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-175000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5889,8 +6138,8 @@
       <c r="L101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -5919,66 +6168,72 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-149500</v>
+      </c>
+      <c r="E102" s="3">
         <v>36100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>108100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>19500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-18900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-64000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-54400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>40700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>391000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-40500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-283600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>257300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-214900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-199400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-755300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>558200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>56600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-67000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-50700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>30900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NIC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NIC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="92">
   <si>
     <t>NIC</t>
   </si>
@@ -656,178 +656,184 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>103200</v>
+      </c>
+      <c r="E8" s="3">
         <v>101900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>94700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>87900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>91400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>90000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>83600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>81500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>87700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>77600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>75400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>31800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>85800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>70700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>59500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>57900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>57600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>38700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>38300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>36900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>38000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>37300</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -894,47 +900,50 @@
       <c r="X9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>103200</v>
+      </c>
+      <c r="E10" s="3">
         <v>101900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>94700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>87900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>91400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>90000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>83600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>81500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>87700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>77600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>75400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>31800</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>5</v>
       </c>
@@ -962,8 +971,11 @@
       <c r="X10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -988,8 +1000,9 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1056,8 +1069,11 @@
       <c r="X12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1124,13 +1140,16 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
+      <c r="D14" s="3">
+        <v>2000</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>5</v>
@@ -1150,21 +1169,21 @@
       <c r="J14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>200</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
@@ -1192,76 +1211,82 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E15" s="3">
         <v>3600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>3500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>3900</v>
       </c>
-      <c r="G15" s="3">
-        <v>5800</v>
-      </c>
       <c r="H15" s="3">
-        <v>4400</v>
+        <v>3300</v>
       </c>
       <c r="I15" s="3">
         <v>4400</v>
       </c>
       <c r="J15" s="3">
+        <v>4400</v>
+      </c>
+      <c r="K15" s="3">
         <v>4800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>8300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>3900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>5100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>4200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-2200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-1300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-1400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-1100</v>
-      </c>
-      <c r="T15" s="3">
-        <v>-800</v>
       </c>
       <c r="U15" s="3">
         <v>-800</v>
       </c>
       <c r="V15" s="3">
-        <v>-900</v>
+        <v>-800</v>
       </c>
       <c r="W15" s="3">
         <v>-900</v>
       </c>
       <c r="X15" s="3">
+        <v>-900</v>
+      </c>
+      <c r="Y15" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1283,144 +1308,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>48800</v>
+      </c>
+      <c r="E17" s="3">
         <v>47700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>47400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>45300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>45600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>46500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>44100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>44300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>47500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>42300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>41800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>42000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>19500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>16300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>54500</v>
+      </c>
+      <c r="E18" s="3">
         <v>54300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>47300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>42600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>45800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>43500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>39500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>37200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>40200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>35300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>33600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-10200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>66300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>54400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>54300</v>
-      </c>
-      <c r="R18" s="3">
-        <v>53500</v>
       </c>
       <c r="S18" s="3">
         <v>53500</v>
       </c>
       <c r="T18" s="3">
+        <v>53500</v>
+      </c>
+      <c r="U18" s="3">
         <v>35100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>35600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>33700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>34000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>32600</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1445,144 +1477,151 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E20" s="3">
         <v>2400</v>
-      </c>
-      <c r="E20" s="3">
-        <v>2500</v>
       </c>
       <c r="F20" s="3">
         <v>2500</v>
       </c>
       <c r="G20" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H20" s="3">
         <v>2600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>3500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>3100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-29200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-29500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-22400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-21600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-31700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-25000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-10600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-9500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-9800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>56200</v>
+      </c>
+      <c r="E21" s="3">
         <v>55400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>48300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>44000</v>
       </c>
-      <c r="G21" s="3">
-        <v>49000</v>
-      </c>
       <c r="H21" s="3">
+        <v>46600</v>
+      </c>
+      <c r="I21" s="3">
         <v>45200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>41200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>39100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>45700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>35700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>35600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-8700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>42000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>30000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>37000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>38700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>26400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>14200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>27500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>26900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>27400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>27200</v>
       </c>
     </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1619,8 +1658,8 @@
       <c r="N22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1649,144 +1688,153 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>50200</v>
+      </c>
+      <c r="E23" s="3">
         <v>51800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>44800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>40100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>43200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>40800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>36700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>34300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>37400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>31800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>30500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-13100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>37100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>24800</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>31900</v>
       </c>
       <c r="R23" s="3">
         <v>31900</v>
       </c>
       <c r="S23" s="3">
+        <v>31900</v>
+      </c>
+      <c r="T23" s="3">
         <v>21800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>10100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>25000</v>
-      </c>
-      <c r="V23" s="3">
-        <v>24200</v>
       </c>
       <c r="W23" s="3">
         <v>24200</v>
       </c>
       <c r="X23" s="3">
+        <v>24200</v>
+      </c>
+      <c r="Y23" s="3">
         <v>24600</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E24" s="3">
         <v>10100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>8700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>7600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>8700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>8300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>7500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>6500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>6800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>14700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>7900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-4200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>9500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>6300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>7900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>7700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>5500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>6700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>5900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>6100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>6400</v>
       </c>
     </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1853,144 +1901,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>40300</v>
+      </c>
+      <c r="E26" s="3">
         <v>41700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>36000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>32600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>34500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>32500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>29300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>27800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>30700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>17200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>22600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-8900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>27600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>18500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>24000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>24200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>16300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>7800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>18300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>18200</v>
-      </c>
-      <c r="W26" s="3">
-        <v>18100</v>
       </c>
       <c r="X26" s="3">
         <v>18100</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3">
+        <v>18100</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>40300</v>
+      </c>
+      <c r="E27" s="3">
         <v>41700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>36000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>32600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>34500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>32500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>29300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>27800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>30700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>17200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>22600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-8900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>27600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>18500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>24000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>24200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>16300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>7800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>18300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>18200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>18000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2057,8 +2114,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2125,8 +2185,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2193,8 +2256,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2261,144 +2327,153 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2400</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-2500</v>
       </c>
       <c r="F32" s="3">
         <v>-2500</v>
       </c>
       <c r="G32" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="H32" s="3">
         <v>-2600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-3500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-3100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>29200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>29500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>22400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>21600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>31700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>25000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>10600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>9500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>9800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>8000</v>
       </c>
     </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>40300</v>
+      </c>
+      <c r="E33" s="3">
         <v>41700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>36000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>32600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>34500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>32500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>29300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>27800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>30700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>17200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>22600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-8900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>27600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>18500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>24000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>24200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>16300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>7800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>18300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>18200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>18000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2465,149 +2540,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>40300</v>
+      </c>
+      <c r="E35" s="3">
         <v>41700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>36000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>32600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>34500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>32500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>29300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>27800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>30700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>17200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>22600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-8900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>27600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>18500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>24000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>24200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>16300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>7800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>18300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>18200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>18000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2632,8 +2716,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2658,76 +2743,80 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>660200</v>
+      </c>
+      <c r="E41" s="3">
         <v>474000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>422600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>572200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>536000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>428000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>408500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>427400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>491400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>545900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>505200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>114200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>133700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>132000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>111700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>203400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>231300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>241700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>101000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>88600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>118000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>100900</v>
       </c>
     </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2741,61 +2830,64 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>3200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>3900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>5600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>6400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>7600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>9800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>11300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>98800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>399000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>138100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>266500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>430000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1171600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>748200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>702800</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>742000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>812300</v>
       </c>
     </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2832,8 +2924,8 @@
       <c r="N43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
+      <c r="O43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P43" s="3">
         <v>0</v>
@@ -2862,47 +2954,50 @@
       <c r="X43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>700</v>
+      </c>
+      <c r="E44" s="3">
         <v>800</v>
-      </c>
-      <c r="E44" s="3">
-        <v>900</v>
       </c>
       <c r="F44" s="3">
         <v>900</v>
       </c>
       <c r="G44" s="3">
+        <v>900</v>
+      </c>
+      <c r="H44" s="3">
         <v>700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2000</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
       <c r="P44" s="3">
         <v>0</v>
       </c>
@@ -2930,47 +3025,50 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>26600</v>
+      </c>
+      <c r="E45" s="3">
         <v>27800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>26800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>26200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>25000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>30900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>32700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>50100</v>
-      </c>
-      <c r="K45" s="3">
-        <v>24200</v>
       </c>
       <c r="L45" s="3">
         <v>24200</v>
       </c>
       <c r="M45" s="3">
+        <v>24200</v>
+      </c>
+      <c r="N45" s="3">
         <v>21500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>21800</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
       <c r="P45" s="3">
         <v>0</v>
       </c>
@@ -2998,47 +3096,50 @@
       <c r="X45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>701100</v>
+      </c>
+      <c r="E46" s="3">
         <v>513800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>460300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>607400</v>
       </c>
-      <c r="G46" s="3">
-        <v>570400</v>
-      </c>
       <c r="H46" s="3">
+        <v>569400</v>
+      </c>
+      <c r="I46" s="3">
         <v>474100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>455700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>489400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>527500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>586200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>541900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>154200</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
       <c r="P46" s="3">
         <v>0</v>
       </c>
@@ -3066,47 +3167,50 @@
       <c r="X46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>889500</v>
+      </c>
+      <c r="E47" s="3">
         <v>889400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>875400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>863400</v>
       </c>
-      <c r="G47" s="3">
-        <v>834200</v>
-      </c>
       <c r="H47" s="3">
+        <v>835200</v>
+      </c>
+      <c r="I47" s="3">
         <v>853100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>827500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>831600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>827000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>819100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>946300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1048000</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
       <c r="P47" s="3">
         <v>0</v>
       </c>
@@ -3134,144 +3238,153 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>120500</v>
+      </c>
+      <c r="E48" s="3">
         <v>121700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>123700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>125300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>127000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>123600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>121000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>120000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>118800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>117700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>117300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>112600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>109000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>106600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>96700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>94300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>94600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>83500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>61600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>59400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>59900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>64200</v>
       </c>
     </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>395600</v>
+      </c>
+      <c r="E49" s="3">
         <v>396100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>409100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>398500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>400100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>400800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>402400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>404400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>406000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>408100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>410400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>412800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>415500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>426500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>350600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>351900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>353100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>283100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>185200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>185400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>185600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>185700</v>
       </c>
     </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3338,8 +3451,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3406,47 +3522,50 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>310900</v>
+      </c>
+      <c r="E52" s="3">
         <v>302400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>291600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>302600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>304800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>294600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>286700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>268100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>299100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>308900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>306900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>303500</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
       <c r="P52" s="3">
         <v>0</v>
       </c>
@@ -3474,8 +3593,11 @@
       <c r="X52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3542,76 +3664,82 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>9185100</v>
+      </c>
+      <c r="E54" s="3">
         <v>9029400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8930800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8975200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8796800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8637100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8557000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8446700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8468700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8416200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8482600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8192400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>8764000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>8895900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7370300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>7320200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7695000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6407800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>4587300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>4543800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>4551800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>4706400</v>
       </c>
     </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3636,8 +3764,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3662,81 +3791,85 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7730800</v>
+      </c>
+      <c r="E57" s="3">
         <v>7611500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7541700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7572200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7403700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7260000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7241100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7165700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7197800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7182400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7198600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6928600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>70200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>56300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>47600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>45800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>68700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>58000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>43800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>49200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>48300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>48900</v>
       </c>
     </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
@@ -3745,7 +3878,7 @@
         <v>0</v>
       </c>
       <c r="G58" s="3">
-        <v>2200</v>
+        <v>0</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
@@ -3763,13 +3896,13 @@
         <v>0</v>
       </c>
       <c r="M58" s="3">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="N58" s="3">
         <v>50000</v>
       </c>
       <c r="O58" s="3">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
@@ -3798,8 +3931,11 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3836,8 +3972,8 @@
       <c r="N59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O59" s="3">
-        <v>0</v>
+      <c r="O59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P59" s="3">
         <v>0</v>
@@ -3866,47 +4002,50 @@
       <c r="X59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7740900</v>
+      </c>
+      <c r="E60" s="3">
         <v>7619800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7550500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7580200</v>
       </c>
-      <c r="G60" s="3">
-        <v>7413700</v>
-      </c>
       <c r="H60" s="3">
+        <v>7411500</v>
+      </c>
+      <c r="I60" s="3">
         <v>7326600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7249900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7173500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7205600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7189400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7254900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6982800</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
       <c r="P60" s="3">
         <v>0</v>
       </c>
@@ -3934,115 +4073,121 @@
       <c r="X60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>138500</v>
+      </c>
+      <c r="E61" s="3">
         <v>134600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>134300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>156600</v>
       </c>
-      <c r="G61" s="3">
-        <v>168100</v>
-      </c>
       <c r="H61" s="3">
+        <v>161400</v>
+      </c>
+      <c r="I61" s="3">
         <v>161200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>162400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>162300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>166900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>197800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>197600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>197400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>192300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>192200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>192000</v>
-      </c>
-      <c r="R61" s="3">
-        <v>191900</v>
       </c>
       <c r="S61" s="3">
         <v>191900</v>
       </c>
       <c r="T61" s="3">
+        <v>191900</v>
+      </c>
+      <c r="U61" s="3">
         <v>124200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>25100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>25000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>24900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>376800</v>
       </c>
     </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>48000</v>
+      </c>
+      <c r="E62" s="3">
         <v>60100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>55900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>55200</v>
       </c>
-      <c r="G62" s="3">
-        <v>42200</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I62" s="3">
+      <c r="H62" s="3">
+        <v>51100</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J62" s="3">
         <v>53300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>47300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>57200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>54500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>52500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>50300</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
       <c r="P62" s="3">
         <v>0</v>
       </c>
@@ -4070,8 +4215,11 @@
       <c r="X62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4138,8 +4286,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4206,8 +4357,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4274,76 +4428,82 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7927400</v>
+      </c>
+      <c r="E66" s="3">
         <v>7814500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7740700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7792000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7623900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7487800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7465600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7383000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7429700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7441700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>7505000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>7230600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7791400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>7957500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>6530900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>6483900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>6803100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5678500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4028000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3993800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4012600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4168300</v>
       </c>
     </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4368,8 +4528,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4436,8 +4597,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4504,8 +4668,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4572,8 +4739,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4640,76 +4810,82 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>697800</v>
+      </c>
+      <c r="E72" s="3">
         <v>662300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>625200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>594100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>565800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>535600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>507400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>482300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>458300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>431300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>417900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>399000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>407900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>380300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>361800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>337800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>313600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>297300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>289500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>271200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>253000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>235000</v>
       </c>
     </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4776,8 +4952,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4844,8 +5023,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4912,76 +5094,82 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1257700</v>
+      </c>
+      <c r="E76" s="3">
         <v>1215000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1190100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1183300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1172900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1149300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1091400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1063700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1039000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>974500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>977600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>961800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>972500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>938500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>839400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>836300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>891900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>729300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>559400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>550000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>539200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>538100</v>
       </c>
     </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5048,149 +5236,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>40300</v>
+      </c>
+      <c r="E81" s="3">
         <v>41700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>36000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>32600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>34500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>32500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>29300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>27800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>30700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>17200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>22600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-8900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>27600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>18500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>24000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>24200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>16300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>7800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>18300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>18200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>18000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5215,76 +5412,80 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>2700</v>
+        <v>3300</v>
       </c>
       <c r="E83" s="3">
         <v>2700</v>
       </c>
       <c r="F83" s="3">
+        <v>2700</v>
+      </c>
+      <c r="G83" s="3">
         <v>3000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>5300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>5200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>5000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>6800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>4600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>4100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>2500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>2700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>3100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5351,8 +5552,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5419,8 +5623,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5487,8 +5694,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5555,8 +5765,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5623,76 +5836,82 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E89" s="3">
         <v>45900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>38900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>41800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>33400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>39600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>37300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>23400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>37800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>21800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>32800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>15500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>30000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>38000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>27400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>21900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>45400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>9200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>4800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>38200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>14600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>44100</v>
       </c>
     </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5717,76 +5936,80 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-3100</v>
       </c>
       <c r="E91" s="3">
-        <v>-500</v>
+        <v>0</v>
       </c>
       <c r="F91" s="3">
         <v>-500</v>
       </c>
       <c r="G91" s="3">
-        <v>-5300</v>
+        <v>-500</v>
       </c>
       <c r="H91" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="I91" s="3">
         <v>-4900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-6900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-5900</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-3200</v>
       </c>
       <c r="U91" s="3">
         <v>-3200</v>
       </c>
       <c r="V91" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="W91" s="3">
         <v>-500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5853,8 +6076,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5921,76 +6147,82 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>45400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-38100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-99800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-138200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-70800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-41000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-127700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-49000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-78700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>88700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>92700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>488800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-134500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-169600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-283100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>70900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-637600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>324600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>24600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-82200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>109700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-19200</v>
       </c>
     </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6015,34 +6247,35 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E96" s="3">
         <v>4700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>4900</v>
-      </c>
-      <c r="F96" s="3">
-        <v>4300</v>
       </c>
       <c r="G96" s="3">
         <v>4300</v>
       </c>
       <c r="H96" s="3">
-        <v>4200</v>
+        <v>4300</v>
       </c>
       <c r="I96" s="3">
         <v>4200</v>
       </c>
       <c r="J96" s="3">
+        <v>4200</v>
+      </c>
+      <c r="K96" s="3">
         <v>3800</v>
-      </c>
-      <c r="K96" s="3">
-        <v>3700</v>
       </c>
       <c r="L96" s="3">
         <v>3700</v>
@@ -6050,11 +6283,11 @@
       <c r="M96" s="3">
         <v>3700</v>
       </c>
-      <c r="N96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="N96" s="3">
+        <v>3700</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -6083,8 +6316,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6151,8 +6387,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6219,8 +6458,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6287,76 +6529,82 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>113900</v>
+      </c>
+      <c r="E100" s="3">
         <v>43600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-88600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>132500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>145400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>20800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>71500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-38400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-13500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-69900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>265500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-544900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-179100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>388900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>40800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-292200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-163100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>224300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>27200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-23100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-175000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6393,8 +6641,8 @@
       <c r="N101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -6423,72 +6671,78 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>186300</v>
+      </c>
+      <c r="E102" s="3">
         <v>51300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-149500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>36100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>108100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>19500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-18900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-64000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-54400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>40700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>391000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-40500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-283600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>257300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-214900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-199400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-755300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>558200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>56600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-67000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-50700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>30900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NIC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NIC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="92">
   <si>
     <t>NIC</t>
   </si>
@@ -656,184 +656,191 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>128800</v>
+      </c>
+      <c r="E8" s="3">
         <v>103200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>101900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>94700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>87900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>91400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>90000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>83600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>81500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>87700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>77600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>75400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>31800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>85800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>70700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>59500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>57900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>57600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>38700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>38300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>36900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>38000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>37300</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -903,50 +910,53 @@
       <c r="Y9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>128800</v>
+      </c>
+      <c r="E10" s="3">
         <v>103200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>101900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>94700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>87900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>91400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>90000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>83600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>81500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>87700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>77600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>75400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>31800</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>5</v>
       </c>
@@ -974,8 +984,11 @@
       <c r="Y10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1001,8 +1014,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1072,8 +1086,11 @@
       <c r="Y12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1143,17 +1160,20 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>40700</v>
+      </c>
+      <c r="E14" s="3">
         <v>2000</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1172,21 +1192,21 @@
       <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>200</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
@@ -1214,79 +1234,85 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E15" s="3">
         <v>4000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>3600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>3500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>3900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3300</v>
-      </c>
-      <c r="I15" s="3">
-        <v>4400</v>
       </c>
       <c r="J15" s="3">
         <v>4400</v>
       </c>
       <c r="K15" s="3">
+        <v>4400</v>
+      </c>
+      <c r="L15" s="3">
         <v>4800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>8300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>3900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>5100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>4200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-1600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-1300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-1400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-1100</v>
-      </c>
-      <c r="U15" s="3">
-        <v>-800</v>
       </c>
       <c r="V15" s="3">
         <v>-800</v>
       </c>
       <c r="W15" s="3">
-        <v>-900</v>
+        <v>-800</v>
       </c>
       <c r="X15" s="3">
         <v>-900</v>
       </c>
       <c r="Y15" s="3">
+        <v>-900</v>
+      </c>
+      <c r="Z15" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1309,150 +1335,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>63700</v>
+      </c>
+      <c r="E17" s="3">
         <v>48800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>47700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>47400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>45300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>45600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>46500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>44100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>44300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>47500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>42300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>41800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>42000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>19500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>16300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>65100</v>
+      </c>
+      <c r="E18" s="3">
         <v>54500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>54300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>47300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>42600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>45800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>43500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>39500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>37200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>40200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>35300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>33600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-10200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>66300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>54400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>54300</v>
-      </c>
-      <c r="S18" s="3">
-        <v>53500</v>
       </c>
       <c r="T18" s="3">
         <v>53500</v>
       </c>
       <c r="U18" s="3">
+        <v>53500</v>
+      </c>
+      <c r="V18" s="3">
         <v>35100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>35600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>33700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>34000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>32600</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1478,150 +1511,157 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E20" s="3">
         <v>2300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2400</v>
-      </c>
-      <c r="F20" s="3">
-        <v>2500</v>
       </c>
       <c r="G20" s="3">
         <v>2500</v>
       </c>
       <c r="H20" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I20" s="3">
         <v>2600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>3500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>3100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-29200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-29500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-22400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-21600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-31700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-25000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-10600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-9500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-9800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>61900</v>
+      </c>
+      <c r="E21" s="3">
         <v>56200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>55400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>48300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>44000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>46600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>45200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>41200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>39100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>45700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>35700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>35600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-8700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>42000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>30000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>37000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>38700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>26400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>14200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>27500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>26900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>27400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>27200</v>
       </c>
     </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1661,8 +1701,8 @@
       <c r="O22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1691,150 +1731,159 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E23" s="3">
         <v>50200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>51800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>44800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>40100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>43200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>40800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>36700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>34300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>37400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>31800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>30500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-13100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>37100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>24800</v>
-      </c>
-      <c r="R23" s="3">
-        <v>31900</v>
       </c>
       <c r="S23" s="3">
         <v>31900</v>
       </c>
       <c r="T23" s="3">
+        <v>31900</v>
+      </c>
+      <c r="U23" s="3">
         <v>21800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>10100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>25000</v>
-      </c>
-      <c r="W23" s="3">
-        <v>24200</v>
       </c>
       <c r="X23" s="3">
         <v>24200</v>
       </c>
       <c r="Y23" s="3">
+        <v>24200</v>
+      </c>
+      <c r="Z23" s="3">
         <v>24600</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E24" s="3">
         <v>9900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>10100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>8700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>7600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>8700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>8300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>7500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>6500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>6800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>14700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>7900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-4200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>9500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>6300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>7900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>7700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>5500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>6700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>5900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>6100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>6400</v>
       </c>
     </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1904,150 +1953,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E26" s="3">
         <v>40300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>41700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>36000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>32600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>34500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>32500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>29300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>27800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>30700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>17200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>22600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-8900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>27600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>18500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>24000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>24200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>16300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>7800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>18300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>18200</v>
-      </c>
-      <c r="X26" s="3">
-        <v>18100</v>
       </c>
       <c r="Y26" s="3">
         <v>18100</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3">
+        <v>18100</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E27" s="3">
         <v>40300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>41700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>36000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>32600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>34500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>32500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>29300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>27800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>30700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>17200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>22600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-8900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>27600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>18500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>24000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>24200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>16300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>7800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>18300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>18200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>18000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2117,8 +2175,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2188,8 +2249,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2259,8 +2323,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2330,150 +2397,159 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2400</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-2500</v>
       </c>
       <c r="G32" s="3">
         <v>-2500</v>
       </c>
       <c r="H32" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="I32" s="3">
         <v>-2600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-3500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-3100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>29200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>29500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>22400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>21600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>31700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>25000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>10600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>9500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>9800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>8000</v>
       </c>
     </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E33" s="3">
         <v>40300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>41700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>36000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>32600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>34500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>32500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>29300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>27800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>30700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>17200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>22600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-8900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>27600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>18500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>24000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>24200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>16300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>7800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>18300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>18200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>18000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2543,155 +2619,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E35" s="3">
         <v>40300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>41700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>36000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>32600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>34500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>32500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>29300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>27800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>30700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>17200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>22600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-8900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>27600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>18500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>24000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>24200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>16300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>7800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>18300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>18200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>18000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2717,8 +2802,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2744,79 +2830,83 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>615500</v>
+      </c>
+      <c r="E41" s="3">
         <v>660200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>474000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>422600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>572200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>536000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>428000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>408500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>427400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>491400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>545900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>505200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>114200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>133700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>132000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>111700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>203400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>231300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>241700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>101000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>88600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>118000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>100900</v>
       </c>
     </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2836,58 +2926,61 @@
         <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>3200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>3900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>5600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>6400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>7600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>9800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>11300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>98800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>399000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>138100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>266500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>430000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>1171600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>748200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>702800</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>742000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>812300</v>
       </c>
     </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2927,8 +3020,8 @@
       <c r="O43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
+      <c r="P43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q43" s="3">
         <v>0</v>
@@ -2957,50 +3050,53 @@
       <c r="Y43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E44" s="3">
         <v>700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>800</v>
-      </c>
-      <c r="F44" s="3">
-        <v>900</v>
       </c>
       <c r="G44" s="3">
         <v>900</v>
       </c>
       <c r="H44" s="3">
+        <v>900</v>
+      </c>
+      <c r="I44" s="3">
         <v>700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2000</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
-      </c>
       <c r="Q44" s="3">
         <v>0</v>
       </c>
@@ -3028,50 +3124,53 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>454900</v>
+      </c>
+      <c r="E45" s="3">
         <v>26600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>27800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>26800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>26200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>25000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>30900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>32700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>50100</v>
-      </c>
-      <c r="L45" s="3">
-        <v>24200</v>
       </c>
       <c r="M45" s="3">
         <v>24200</v>
       </c>
       <c r="N45" s="3">
+        <v>24200</v>
+      </c>
+      <c r="O45" s="3">
         <v>21500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>21800</v>
       </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
       <c r="Q45" s="3">
         <v>0</v>
       </c>
@@ -3099,50 +3198,53 @@
       <c r="Y45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1092900</v>
+      </c>
+      <c r="E46" s="3">
         <v>701100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>513800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>460300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>607400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>569400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>474100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>455700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>489400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>527500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>586200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>541900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>154200</v>
       </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
@@ -3170,50 +3272,53 @@
       <c r="Y46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2033500</v>
+      </c>
+      <c r="E47" s="3">
         <v>889500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>889400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>875400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>863400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>835200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>853100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>827500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>831600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>827000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>819100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>946300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1048000</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
       <c r="Q47" s="3">
         <v>0</v>
       </c>
@@ -3241,150 +3346,159 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>187900</v>
+      </c>
+      <c r="E48" s="3">
         <v>120500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>121700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>123700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>125300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>127000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>123600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>121000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>120000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>118800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>117700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>117300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>112600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>109000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>106600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>96700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>94300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>94600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>83500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>61600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>59400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>59900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>64200</v>
       </c>
     </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>992300</v>
+      </c>
+      <c r="E49" s="3">
         <v>395600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>396100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>409100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>398500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>400100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>400800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>402400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>404400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>406000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>408100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>410400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>412800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>415500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>426500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>350600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>351900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>353100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>283100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>185200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>185400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>185600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>185700</v>
       </c>
     </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3454,8 +3568,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3525,50 +3642,53 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>521600</v>
+      </c>
+      <c r="E52" s="3">
         <v>310900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>302400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>291600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>302600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>304800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>294600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>286700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>268100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>299100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>308900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>306900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>303500</v>
       </c>
-      <c r="P52" s="3">
-        <v>0</v>
-      </c>
       <c r="Q52" s="3">
         <v>0</v>
       </c>
@@ -3596,8 +3716,11 @@
       <c r="Y52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3667,79 +3790,85 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>15574500</v>
+      </c>
+      <c r="E54" s="3">
         <v>9185100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>9029400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8930800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8975200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8796800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8637100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8557000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8446700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8468700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8416200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8482600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>8192400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>8764000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>8895900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>7370300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7320200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>7695000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6407800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>4587300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>4543800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>4551800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>4706400</v>
       </c>
     </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3765,8 +3894,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3792,88 +3922,92 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>12624400</v>
+      </c>
+      <c r="E57" s="3">
         <v>7730800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7611500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7541700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7572200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7403700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7260000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7241100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7165700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7197800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7182400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>7198600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>6928600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>70200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>56300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>47600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>45800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>68700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>58000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>43800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>49200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>48300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>48900</v>
       </c>
     </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>1500</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
       <c r="F58" s="3">
         <v>0</v>
       </c>
@@ -3899,13 +4033,13 @@
         <v>0</v>
       </c>
       <c r="N58" s="3">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="O58" s="3">
         <v>50000</v>
       </c>
       <c r="P58" s="3">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
@@ -3934,13 +4068,16 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>5</v>
+      <c r="D59" s="3">
+        <v>385900</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>5</v>
@@ -3975,8 +4112,8 @@
       <c r="O59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P59" s="3">
-        <v>0</v>
+      <c r="P59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q59" s="3">
         <v>0</v>
@@ -4005,50 +4142,53 @@
       <c r="Y59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>13024600</v>
+      </c>
+      <c r="E60" s="3">
         <v>7740900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7619800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7550500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>7580200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7411500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7326600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7249900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7173500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7205600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7189400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7254900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6982800</v>
       </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
       <c r="Q60" s="3">
         <v>0</v>
       </c>
@@ -4076,121 +4216,127 @@
       <c r="Y60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>180000</v>
+      </c>
+      <c r="E61" s="3">
         <v>138500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>134600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>134300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>156600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>161400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>161200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>162400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>162300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>166900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>197800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>197600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>197400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>192300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>192200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>192000</v>
-      </c>
-      <c r="S61" s="3">
-        <v>191900</v>
       </c>
       <c r="T61" s="3">
         <v>191900</v>
       </c>
       <c r="U61" s="3">
+        <v>191900</v>
+      </c>
+      <c r="V61" s="3">
         <v>124200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>25100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>25000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>24900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>376800</v>
       </c>
     </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>113100</v>
+      </c>
+      <c r="E62" s="3">
         <v>48000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>60100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>55900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>55200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>51100</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="J62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K62" s="3">
         <v>53300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>47300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>57200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>54500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>52500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>50300</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
       <c r="Q62" s="3">
         <v>0</v>
       </c>
@@ -4218,8 +4364,11 @@
       <c r="Y62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4289,8 +4438,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4360,8 +4512,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4431,79 +4586,85 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>13317600</v>
+      </c>
+      <c r="E66" s="3">
         <v>7927400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7814500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7740700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7792000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7623900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7487800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7465600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7383000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7429700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>7441700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>7505000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7230600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>7791400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>7957500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>6530900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>6483900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>6803100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5678500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4028000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3993800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4012600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4168300</v>
       </c>
     </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4529,8 +4690,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4600,8 +4762,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4671,8 +4836,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4742,8 +4910,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4813,79 +4984,85 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>706100</v>
+      </c>
+      <c r="E72" s="3">
         <v>697800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>662300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>625200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>594100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>565800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>535600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>507400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>482300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>458300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>431300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>417900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>399000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>407900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>380300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>361800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>337800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>313600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>297300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>289500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>271200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>253000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>235000</v>
       </c>
     </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4955,8 +5132,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5026,8 +5206,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5097,79 +5280,85 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2256900</v>
+      </c>
+      <c r="E76" s="3">
         <v>1257700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1215000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1190100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1183300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1172900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1149300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1091400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1063700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1039000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>974500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>977600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>961800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>972500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>938500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>839400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>836300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>891900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>729300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>559400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>550000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>539200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>538100</v>
       </c>
     </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5239,155 +5428,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E81" s="3">
         <v>40300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>41700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>36000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>32600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>34500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>32500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>29300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>27800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>30700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>17200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>22600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-8900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>27600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>18500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>24000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>24200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>16300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>7800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>18300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>18200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>18000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5413,79 +5611,83 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E83" s="3">
         <v>3300</v>
-      </c>
-      <c r="E83" s="3">
-        <v>2700</v>
       </c>
       <c r="F83" s="3">
         <v>2700</v>
       </c>
       <c r="G83" s="3">
+        <v>2700</v>
+      </c>
+      <c r="H83" s="3">
         <v>3000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>5200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>5000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>6800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>4600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>4100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>2500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>2700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>3100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5555,8 +5757,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5626,8 +5831,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5697,8 +5905,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5768,8 +5979,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5839,79 +6053,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E89" s="3">
         <v>27000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>45900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>38900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>41800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>33400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>39600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>37300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>23400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>37800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>21800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>32800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>15500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>30000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>38000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>27400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>21900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>45400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>9200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>4800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>38200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>14600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>44100</v>
       </c>
     </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5937,79 +6157,83 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3100</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
-        <v>-500</v>
+        <v>0</v>
       </c>
       <c r="G91" s="3">
         <v>-500</v>
       </c>
       <c r="H91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I91" s="3">
         <v>-5700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-6900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-5900</v>
-      </c>
-      <c r="U91" s="3">
-        <v>-3200</v>
       </c>
       <c r="V91" s="3">
         <v>-3200</v>
       </c>
       <c r="W91" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="X91" s="3">
         <v>-500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6079,8 +6303,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6150,79 +6377,85 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>65800</v>
+      </c>
+      <c r="E94" s="3">
         <v>45400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-38100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-99800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-138200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-70800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-41000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-127700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-49000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-78700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>88700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>92700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>488800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-134500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-169600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-283100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>70900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-637600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>324600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>24600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-82200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>109700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-19200</v>
       </c>
     </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6248,37 +6481,38 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E96" s="3">
         <v>4800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>4700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>4900</v>
-      </c>
-      <c r="G96" s="3">
-        <v>4300</v>
       </c>
       <c r="H96" s="3">
         <v>4300</v>
       </c>
       <c r="I96" s="3">
-        <v>4200</v>
+        <v>4300</v>
       </c>
       <c r="J96" s="3">
         <v>4200</v>
       </c>
       <c r="K96" s="3">
+        <v>4200</v>
+      </c>
+      <c r="L96" s="3">
         <v>3800</v>
-      </c>
-      <c r="L96" s="3">
-        <v>3700</v>
       </c>
       <c r="M96" s="3">
         <v>3700</v>
@@ -6286,11 +6520,11 @@
       <c r="N96" s="3">
         <v>3700</v>
       </c>
-      <c r="O96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3">
+        <v>3700</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -6319,8 +6553,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6390,8 +6627,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6461,8 +6701,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6532,79 +6775,85 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-126900</v>
+      </c>
+      <c r="E100" s="3">
         <v>113900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>43600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-88600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>132500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>145400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>20800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>71500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-38400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-13500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-69900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>265500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-544900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-179100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>388900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>40800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-292200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-163100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>224300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>27200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-23100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-175000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6644,8 +6893,8 @@
       <c r="O101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -6674,75 +6923,81 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-44800</v>
+      </c>
+      <c r="E102" s="3">
         <v>186300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>51300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-149500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>36100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>108100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>19500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-18900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-64000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-54400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>40700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>391000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-40500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-283600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>257300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-214900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-199400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-755300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>558200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>56600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-67000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-50700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>30900</v>
       </c>
     </row>
